--- a/reports/塔防模式_4日战役智能设计器.xlsx
+++ b/reports/塔防模式_4日战役智能设计器.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wh\Documents\arc-nice\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF4A052-A760-41A2-89CE-8A5224B729B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C99EF68-840F-4A9A-827F-1D3A83C033E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="571">
   <si>
     <t>塔防模式｜4 日战役智能设计器</t>
   </si>
@@ -1741,6 +1741,10 @@
   </si>
   <si>
     <t>寒冰史莱姆</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>举盾战斗机器人</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2080,16 +2084,13 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2097,6 +2098,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2230,16 +2234,16 @@
                   <c:v>11750</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>242</c:v>
+                  <c:v>26700</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>308</c:v>
+                  <c:v>38800</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>398</c:v>
+                  <c:v>47200</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>453</c:v>
+                  <c:v>65000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2335,16 +2339,16 @@
                   <c:v>11750</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>242</c:v>
+                  <c:v>26700</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>308</c:v>
+                  <c:v>38800</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>398</c:v>
+                  <c:v>47200</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>453</c:v>
+                  <c:v>65000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2556,16 +2560,16 @@
                   <c:v>2240</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>144</c:v>
+                  <c:v>3120</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>160</c:v>
+                  <c:v>3780</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>176</c:v>
+                  <c:v>3000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>200</c:v>
+                  <c:v>4900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8201,11 +8205,11 @@
       </c>
       <c r="I77" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J77" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K77" s="13">
         <f>第2日!I3</f>
@@ -8269,11 +8273,11 @@
       </c>
       <c r="I78" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J78" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K78" s="13">
         <f>第2日!I3</f>
@@ -8337,11 +8341,11 @@
       </c>
       <c r="I79" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J79" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K79" s="13">
         <f>第2日!I3</f>
@@ -8405,11 +8409,11 @@
       </c>
       <c r="I80" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J80" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K80" s="13">
         <f>第2日!I3</f>
@@ -8473,11 +8477,11 @@
       </c>
       <c r="I81" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J81" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K81" s="13">
         <f>第2日!I3</f>
@@ -8541,11 +8545,11 @@
       </c>
       <c r="I82" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J82" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K82" s="13">
         <f>第2日!I3</f>
@@ -8609,11 +8613,11 @@
       </c>
       <c r="I83" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J83" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K83" s="13">
         <f>第2日!I3</f>
@@ -8677,11 +8681,11 @@
       </c>
       <c r="I84" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J84" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K84" s="13">
         <f>第2日!I3</f>
@@ -8745,11 +8749,11 @@
       </c>
       <c r="I85" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J85" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K85" s="13">
         <f>第2日!I3</f>
@@ -8813,11 +8817,11 @@
       </c>
       <c r="I86" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J86" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K86" s="13">
         <f>第2日!I3</f>
@@ -8881,11 +8885,11 @@
       </c>
       <c r="I87" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J87" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K87" s="13">
         <f>第2日!I3</f>
@@ -8949,11 +8953,11 @@
       </c>
       <c r="I88" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J88" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K88" s="13">
         <f>第2日!I3</f>
@@ -9017,11 +9021,11 @@
       </c>
       <c r="I89" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J89" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K89" s="13">
         <f>第2日!I3</f>
@@ -9085,11 +9089,11 @@
       </c>
       <c r="I90" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J90" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K90" s="13">
         <f>第2日!I3</f>
@@ -9153,11 +9157,11 @@
       </c>
       <c r="I91" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J91" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K91" s="13">
         <f>第2日!I3</f>
@@ -9221,11 +9225,11 @@
       </c>
       <c r="I92" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J92" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K92" s="13">
         <f>第2日!I3</f>
@@ -9289,11 +9293,11 @@
       </c>
       <c r="I93" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J93" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K93" s="13">
         <f>第2日!I3</f>
@@ -9357,11 +9361,11 @@
       </c>
       <c r="I94" s="13">
         <f>第2日!E3</f>
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J94" s="13">
         <f>第2日!G3</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K94" s="13">
         <f>第2日!I3</f>
@@ -9425,7 +9429,7 @@
       </c>
       <c r="I95" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J95" s="13">
         <f>第2日!G32</f>
@@ -9433,7 +9437,7 @@
       </c>
       <c r="K95" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L95" s="13" t="s">
         <v>537</v>
@@ -9493,7 +9497,7 @@
       </c>
       <c r="I96" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J96" s="13">
         <f>第2日!G32</f>
@@ -9501,7 +9505,7 @@
       </c>
       <c r="K96" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L96" s="13" t="s">
         <v>537</v>
@@ -9561,7 +9565,7 @@
       </c>
       <c r="I97" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J97" s="13">
         <f>第2日!G32</f>
@@ -9569,7 +9573,7 @@
       </c>
       <c r="K97" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L97" s="13" t="s">
         <v>537</v>
@@ -9629,7 +9633,7 @@
       </c>
       <c r="I98" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J98" s="13">
         <f>第2日!G32</f>
@@ -9637,7 +9641,7 @@
       </c>
       <c r="K98" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L98" s="13" t="s">
         <v>537</v>
@@ -9697,7 +9701,7 @@
       </c>
       <c r="I99" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J99" s="13">
         <f>第2日!G32</f>
@@ -9705,7 +9709,7 @@
       </c>
       <c r="K99" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L99" s="13" t="s">
         <v>537</v>
@@ -9765,7 +9769,7 @@
       </c>
       <c r="I100" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J100" s="13">
         <f>第2日!G32</f>
@@ -9773,7 +9777,7 @@
       </c>
       <c r="K100" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L100" s="13" t="s">
         <v>537</v>
@@ -9833,7 +9837,7 @@
       </c>
       <c r="I101" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J101" s="13">
         <f>第2日!G32</f>
@@ -9841,7 +9845,7 @@
       </c>
       <c r="K101" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L101" s="13" t="s">
         <v>537</v>
@@ -9901,7 +9905,7 @@
       </c>
       <c r="I102" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J102" s="13">
         <f>第2日!G32</f>
@@ -9909,7 +9913,7 @@
       </c>
       <c r="K102" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L102" s="13" t="s">
         <v>537</v>
@@ -9969,7 +9973,7 @@
       </c>
       <c r="I103" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J103" s="13">
         <f>第2日!G32</f>
@@ -9977,7 +9981,7 @@
       </c>
       <c r="K103" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L103" s="13" t="s">
         <v>537</v>
@@ -10037,7 +10041,7 @@
       </c>
       <c r="I104" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J104" s="13">
         <f>第2日!G32</f>
@@ -10045,7 +10049,7 @@
       </c>
       <c r="K104" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L104" s="13" t="s">
         <v>537</v>
@@ -10105,7 +10109,7 @@
       </c>
       <c r="I105" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J105" s="13">
         <f>第2日!G32</f>
@@ -10113,7 +10117,7 @@
       </c>
       <c r="K105" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L105" s="13" t="s">
         <v>537</v>
@@ -10173,7 +10177,7 @@
       </c>
       <c r="I106" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J106" s="13">
         <f>第2日!G32</f>
@@ -10181,7 +10185,7 @@
       </c>
       <c r="K106" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L106" s="13" t="s">
         <v>537</v>
@@ -10241,7 +10245,7 @@
       </c>
       <c r="I107" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J107" s="13">
         <f>第2日!G32</f>
@@ -10249,7 +10253,7 @@
       </c>
       <c r="K107" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L107" s="13" t="s">
         <v>537</v>
@@ -10309,7 +10313,7 @@
       </c>
       <c r="I108" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J108" s="13">
         <f>第2日!G32</f>
@@ -10317,7 +10321,7 @@
       </c>
       <c r="K108" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L108" s="13" t="s">
         <v>537</v>
@@ -10377,7 +10381,7 @@
       </c>
       <c r="I109" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J109" s="13">
         <f>第2日!G32</f>
@@ -10385,7 +10389,7 @@
       </c>
       <c r="K109" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L109" s="13" t="s">
         <v>537</v>
@@ -10445,7 +10449,7 @@
       </c>
       <c r="I110" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J110" s="13">
         <f>第2日!G32</f>
@@ -10453,7 +10457,7 @@
       </c>
       <c r="K110" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L110" s="13" t="s">
         <v>537</v>
@@ -10513,7 +10517,7 @@
       </c>
       <c r="I111" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J111" s="13">
         <f>第2日!G32</f>
@@ -10521,7 +10525,7 @@
       </c>
       <c r="K111" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L111" s="13" t="s">
         <v>537</v>
@@ -10581,7 +10585,7 @@
       </c>
       <c r="I112" s="13">
         <f>第2日!E32</f>
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J112" s="13">
         <f>第2日!G32</f>
@@ -10589,7 +10593,7 @@
       </c>
       <c r="K112" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="L112" s="13" t="s">
         <v>537</v>
@@ -10649,7 +10653,7 @@
       </c>
       <c r="I113" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J113" s="13">
         <f>第2日!G61</f>
@@ -10657,7 +10661,7 @@
       </c>
       <c r="K113" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L113" s="13" t="s">
         <v>537</v>
@@ -10717,7 +10721,7 @@
       </c>
       <c r="I114" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J114" s="13">
         <f>第2日!G61</f>
@@ -10725,7 +10729,7 @@
       </c>
       <c r="K114" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L114" s="13" t="s">
         <v>537</v>
@@ -10785,7 +10789,7 @@
       </c>
       <c r="I115" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J115" s="13">
         <f>第2日!G61</f>
@@ -10793,7 +10797,7 @@
       </c>
       <c r="K115" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L115" s="13" t="s">
         <v>537</v>
@@ -10853,7 +10857,7 @@
       </c>
       <c r="I116" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J116" s="13">
         <f>第2日!G61</f>
@@ -10861,7 +10865,7 @@
       </c>
       <c r="K116" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L116" s="13" t="s">
         <v>537</v>
@@ -10921,7 +10925,7 @@
       </c>
       <c r="I117" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J117" s="13">
         <f>第2日!G61</f>
@@ -10929,7 +10933,7 @@
       </c>
       <c r="K117" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L117" s="13" t="s">
         <v>537</v>
@@ -10989,7 +10993,7 @@
       </c>
       <c r="I118" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J118" s="13">
         <f>第2日!G61</f>
@@ -10997,7 +11001,7 @@
       </c>
       <c r="K118" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L118" s="13" t="s">
         <v>537</v>
@@ -11057,7 +11061,7 @@
       </c>
       <c r="I119" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J119" s="13">
         <f>第2日!G61</f>
@@ -11065,7 +11069,7 @@
       </c>
       <c r="K119" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L119" s="13" t="s">
         <v>537</v>
@@ -11125,7 +11129,7 @@
       </c>
       <c r="I120" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J120" s="13">
         <f>第2日!G61</f>
@@ -11133,7 +11137,7 @@
       </c>
       <c r="K120" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L120" s="13" t="s">
         <v>537</v>
@@ -11193,7 +11197,7 @@
       </c>
       <c r="I121" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J121" s="13">
         <f>第2日!G61</f>
@@ -11201,7 +11205,7 @@
       </c>
       <c r="K121" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L121" s="13" t="s">
         <v>537</v>
@@ -11261,7 +11265,7 @@
       </c>
       <c r="I122" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J122" s="13">
         <f>第2日!G61</f>
@@ -11269,7 +11273,7 @@
       </c>
       <c r="K122" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L122" s="13" t="s">
         <v>537</v>
@@ -11329,7 +11333,7 @@
       </c>
       <c r="I123" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J123" s="13">
         <f>第2日!G61</f>
@@ -11337,7 +11341,7 @@
       </c>
       <c r="K123" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L123" s="13" t="s">
         <v>537</v>
@@ -11397,7 +11401,7 @@
       </c>
       <c r="I124" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J124" s="13">
         <f>第2日!G61</f>
@@ -11405,7 +11409,7 @@
       </c>
       <c r="K124" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L124" s="13" t="s">
         <v>537</v>
@@ -11465,7 +11469,7 @@
       </c>
       <c r="I125" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J125" s="13">
         <f>第2日!G61</f>
@@ -11473,7 +11477,7 @@
       </c>
       <c r="K125" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L125" s="13" t="s">
         <v>537</v>
@@ -11533,7 +11537,7 @@
       </c>
       <c r="I126" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J126" s="13">
         <f>第2日!G61</f>
@@ -11541,7 +11545,7 @@
       </c>
       <c r="K126" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L126" s="13" t="s">
         <v>537</v>
@@ -11601,7 +11605,7 @@
       </c>
       <c r="I127" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J127" s="13">
         <f>第2日!G61</f>
@@ -11609,7 +11613,7 @@
       </c>
       <c r="K127" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L127" s="13" t="s">
         <v>537</v>
@@ -11669,7 +11673,7 @@
       </c>
       <c r="I128" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J128" s="13">
         <f>第2日!G61</f>
@@ -11677,7 +11681,7 @@
       </c>
       <c r="K128" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L128" s="13" t="s">
         <v>537</v>
@@ -11737,7 +11741,7 @@
       </c>
       <c r="I129" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J129" s="13">
         <f>第2日!G61</f>
@@ -11745,7 +11749,7 @@
       </c>
       <c r="K129" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L129" s="13" t="s">
         <v>537</v>
@@ -11805,7 +11809,7 @@
       </c>
       <c r="I130" s="13">
         <f>第2日!E61</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J130" s="13">
         <f>第2日!G61</f>
@@ -11813,7 +11817,7 @@
       </c>
       <c r="K130" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="L130" s="13" t="s">
         <v>537</v>
@@ -11873,7 +11877,7 @@
       </c>
       <c r="I131" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J131" s="13">
         <f>第2日!G90</f>
@@ -11941,7 +11945,7 @@
       </c>
       <c r="I132" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J132" s="13">
         <f>第2日!G90</f>
@@ -12009,7 +12013,7 @@
       </c>
       <c r="I133" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J133" s="13">
         <f>第2日!G90</f>
@@ -12077,7 +12081,7 @@
       </c>
       <c r="I134" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J134" s="13">
         <f>第2日!G90</f>
@@ -12145,7 +12149,7 @@
       </c>
       <c r="I135" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J135" s="13">
         <f>第2日!G90</f>
@@ -12213,7 +12217,7 @@
       </c>
       <c r="I136" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J136" s="13">
         <f>第2日!G90</f>
@@ -12281,7 +12285,7 @@
       </c>
       <c r="I137" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J137" s="13">
         <f>第2日!G90</f>
@@ -12349,7 +12353,7 @@
       </c>
       <c r="I138" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J138" s="13">
         <f>第2日!G90</f>
@@ -12417,7 +12421,7 @@
       </c>
       <c r="I139" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J139" s="13">
         <f>第2日!G90</f>
@@ -12485,7 +12489,7 @@
       </c>
       <c r="I140" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J140" s="13">
         <f>第2日!G90</f>
@@ -12553,7 +12557,7 @@
       </c>
       <c r="I141" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J141" s="13">
         <f>第2日!G90</f>
@@ -12621,7 +12625,7 @@
       </c>
       <c r="I142" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J142" s="13">
         <f>第2日!G90</f>
@@ -12689,7 +12693,7 @@
       </c>
       <c r="I143" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J143" s="13">
         <f>第2日!G90</f>
@@ -12757,7 +12761,7 @@
       </c>
       <c r="I144" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J144" s="13">
         <f>第2日!G90</f>
@@ -12825,7 +12829,7 @@
       </c>
       <c r="I145" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J145" s="13">
         <f>第2日!G90</f>
@@ -12893,7 +12897,7 @@
       </c>
       <c r="I146" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J146" s="13">
         <f>第2日!G90</f>
@@ -12961,7 +12965,7 @@
       </c>
       <c r="I147" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J147" s="13">
         <f>第2日!G90</f>
@@ -13029,7 +13033,7 @@
       </c>
       <c r="I148" s="13">
         <f>第2日!E90</f>
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J148" s="13">
         <f>第2日!G90</f>
@@ -13097,7 +13101,7 @@
       </c>
       <c r="I149" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J149" s="13">
         <f>第3日!G3</f>
@@ -13122,11 +13126,11 @@
       </c>
       <c r="P149" s="13" t="str">
         <f>IF(第3日!B7="","",IFERROR(VLOOKUP(第3日!B7,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_basic</v>
+        <v>slime_golden</v>
       </c>
       <c r="Q149" s="13">
         <f>IF(第3日!B7="","",第3日!C7)</f>
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="R149" s="13">
         <v>-1</v>
@@ -13165,7 +13169,7 @@
       </c>
       <c r="I150" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J150" s="13">
         <f>第3日!G3</f>
@@ -13190,11 +13194,11 @@
       </c>
       <c r="P150" s="13" t="str">
         <f>IF(第3日!B8="","",IFERROR(VLOOKUP(第3日!B8,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_fast</v>
+        <v>capoo_ak47</v>
       </c>
       <c r="Q150" s="13">
         <f>IF(第3日!B8="","",第3日!C8)</f>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="R150" s="13">
         <v>-1</v>
@@ -13233,7 +13237,7 @@
       </c>
       <c r="I151" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J151" s="13">
         <f>第3日!G3</f>
@@ -13258,7 +13262,7 @@
       </c>
       <c r="P151" s="13" t="str">
         <f>IF(第3日!B9="","",IFERROR(VLOOKUP(第3日!B9,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_shell</v>
+        <v>stone_golem</v>
       </c>
       <c r="Q151" s="13">
         <f>IF(第3日!B9="","",第3日!C9)</f>
@@ -13301,7 +13305,7 @@
       </c>
       <c r="I152" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J152" s="13">
         <f>第3日!G3</f>
@@ -13326,11 +13330,11 @@
       </c>
       <c r="P152" s="13" t="str">
         <f>IF(第3日!B10="","",IFERROR(VLOOKUP(第3日!B10,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_bomber</v>
+        <v>stone_golem_elite</v>
       </c>
       <c r="Q152" s="13">
         <f>IF(第3日!B10="","",第3日!C10)</f>
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="R152" s="13">
         <v>-1</v>
@@ -13369,7 +13373,7 @@
       </c>
       <c r="I153" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J153" s="13">
         <f>第3日!G3</f>
@@ -13394,11 +13398,11 @@
       </c>
       <c r="P153" s="13" t="str">
         <f>IF(第3日!B11="","",IFERROR(VLOOKUP(第3日!B11,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_purple_bomber</v>
+        <v>yuanshi_insect_fire_ranged</v>
       </c>
       <c r="Q153" s="13">
         <f>IF(第3日!B11="","",第3日!C11)</f>
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="R153" s="13">
         <v>-1</v>
@@ -13437,7 +13441,7 @@
       </c>
       <c r="I154" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J154" s="13">
         <f>第3日!G3</f>
@@ -13462,11 +13466,11 @@
       </c>
       <c r="P154" s="13" t="str">
         <f>IF(第3日!B12="","",IFERROR(VLOOKUP(第3日!B12,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_fire_ranged</v>
+        <v>cardboard_monster</v>
       </c>
       <c r="Q154" s="13">
         <f>IF(第3日!B12="","",第3日!C12)</f>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="R154" s="13">
         <v>-1</v>
@@ -13505,7 +13509,7 @@
       </c>
       <c r="I155" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J155" s="13">
         <f>第3日!G3</f>
@@ -13530,11 +13534,11 @@
       </c>
       <c r="P155" s="13" t="str">
         <f>IF(第3日!B13="","",IFERROR(VLOOKUP(第3日!B13,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_green_shell</v>
+        <v>combat_robot_ninja</v>
       </c>
       <c r="Q155" s="13">
         <f>IF(第3日!B13="","",第3日!C13)</f>
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="R155" s="13">
         <v>-1</v>
@@ -13573,7 +13577,7 @@
       </c>
       <c r="I156" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J156" s="13">
         <f>第3日!G3</f>
@@ -13598,11 +13602,11 @@
       </c>
       <c r="P156" s="13" t="str">
         <f>IF(第3日!B14="","",IFERROR(VLOOKUP(第3日!B14,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_guardian</v>
+        <v>combat_robot_ninja_elite</v>
       </c>
       <c r="Q156" s="13">
         <f>IF(第3日!B14="","",第3日!C14)</f>
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="R156" s="13">
         <v>-1</v>
@@ -13641,7 +13645,7 @@
       </c>
       <c r="I157" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J157" s="13">
         <f>第3日!G3</f>
@@ -13666,11 +13670,11 @@
       </c>
       <c r="P157" s="13" t="str">
         <f>IF(第3日!B15="","",IFERROR(VLOOKUP(第3日!B15,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>capoo_knight</v>
+        <v>yuanshi_insect_guardian</v>
       </c>
       <c r="Q157" s="13">
         <f>IF(第3日!B15="","",第3日!C15)</f>
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="R157" s="13">
         <v>-1</v>
@@ -13709,7 +13713,7 @@
       </c>
       <c r="I158" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J158" s="13">
         <f>第3日!G3</f>
@@ -13734,18 +13738,18 @@
       </c>
       <c r="P158" s="13" t="str">
         <f>IF(第3日!B16="","",IFERROR(VLOOKUP(第3日!B16,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q158" s="13" t="str">
+        <v>capoo_knight_elite</v>
+      </c>
+      <c r="Q158" s="13">
         <f>IF(第3日!B16="","",第3日!C16)</f>
-        <v/>
+        <v>400</v>
       </c>
       <c r="R158" s="13">
         <v>-1</v>
       </c>
       <c r="S158" s="13" t="str">
         <f>IF(第3日!B16="","",第3日!I16)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="159" spans="1:19" ht="16.5">
@@ -13777,7 +13781,7 @@
       </c>
       <c r="I159" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J159" s="13">
         <f>第3日!G3</f>
@@ -13802,18 +13806,18 @@
       </c>
       <c r="P159" s="13" t="str">
         <f>IF(第3日!B17="","",IFERROR(VLOOKUP(第3日!B17,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q159" s="13" t="str">
+        <v>combat_robot_drone_operator_elite</v>
+      </c>
+      <c r="Q159" s="13">
         <f>IF(第3日!B17="","",第3日!C17)</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="R159" s="13">
         <v>-1</v>
       </c>
       <c r="S159" s="13" t="str">
         <f>IF(第3日!B17="","",第3日!I17)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="160" spans="1:19" ht="16.5">
@@ -13845,7 +13849,7 @@
       </c>
       <c r="I160" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J160" s="13">
         <f>第3日!G3</f>
@@ -13870,18 +13874,18 @@
       </c>
       <c r="P160" s="13" t="str">
         <f>IF(第3日!B18="","",IFERROR(VLOOKUP(第3日!B18,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q160" s="13" t="str">
+        <v>combat_robot</v>
+      </c>
+      <c r="Q160" s="13">
         <f>IF(第3日!B18="","",第3日!C18)</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="R160" s="13">
         <v>-1</v>
       </c>
       <c r="S160" s="13" t="str">
         <f>IF(第3日!B18="","",第3日!I18)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="161" spans="1:19" ht="16.5">
@@ -13913,7 +13917,7 @@
       </c>
       <c r="I161" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J161" s="13">
         <f>第3日!G3</f>
@@ -13938,18 +13942,18 @@
       </c>
       <c r="P161" s="13" t="str">
         <f>IF(第3日!B19="","",IFERROR(VLOOKUP(第3日!B19,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q161" s="13" t="str">
+        <v>combat_robot_shield_bearer</v>
+      </c>
+      <c r="Q161" s="13">
         <f>IF(第3日!B19="","",第3日!C19)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="R161" s="13">
         <v>-1</v>
       </c>
       <c r="S161" s="13" t="str">
         <f>IF(第3日!B19="","",第3日!I19)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="162" spans="1:19" ht="16.5">
@@ -13981,7 +13985,7 @@
       </c>
       <c r="I162" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J162" s="13">
         <f>第3日!G3</f>
@@ -14049,7 +14053,7 @@
       </c>
       <c r="I163" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J163" s="13">
         <f>第3日!G3</f>
@@ -14117,7 +14121,7 @@
       </c>
       <c r="I164" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J164" s="13">
         <f>第3日!G3</f>
@@ -14185,7 +14189,7 @@
       </c>
       <c r="I165" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J165" s="13">
         <f>第3日!G3</f>
@@ -14253,7 +14257,7 @@
       </c>
       <c r="I166" s="13">
         <f>第3日!E3</f>
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="J166" s="13">
         <f>第3日!G3</f>
@@ -14321,7 +14325,7 @@
       </c>
       <c r="I167" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J167" s="13">
         <f>第3日!G32</f>
@@ -14346,11 +14350,11 @@
       </c>
       <c r="P167" s="13" t="str">
         <f>IF(第3日!B36="","",IFERROR(VLOOKUP(第3日!B36,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_basic</v>
+        <v>slime_golden</v>
       </c>
       <c r="Q167" s="13">
         <f>IF(第3日!B36="","",第3日!C36)</f>
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="R167" s="13">
         <v>-1</v>
@@ -14389,7 +14393,7 @@
       </c>
       <c r="I168" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J168" s="13">
         <f>第3日!G32</f>
@@ -14414,11 +14418,11 @@
       </c>
       <c r="P168" s="13" t="str">
         <f>IF(第3日!B37="","",IFERROR(VLOOKUP(第3日!B37,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_fast</v>
+        <v>capoo_rpg</v>
       </c>
       <c r="Q168" s="13">
         <f>IF(第3日!B37="","",第3日!C37)</f>
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="R168" s="13">
         <v>-1</v>
@@ -14457,7 +14461,7 @@
       </c>
       <c r="I169" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J169" s="13">
         <f>第3日!G32</f>
@@ -14482,11 +14486,11 @@
       </c>
       <c r="P169" s="13" t="str">
         <f>IF(第3日!B38="","",IFERROR(VLOOKUP(第3日!B38,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_shell</v>
+        <v>stone_golem</v>
       </c>
       <c r="Q169" s="13">
         <f>IF(第3日!B38="","",第3日!C38)</f>
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="R169" s="13">
         <v>-1</v>
@@ -14525,7 +14529,7 @@
       </c>
       <c r="I170" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J170" s="13">
         <f>第3日!G32</f>
@@ -14550,11 +14554,11 @@
       </c>
       <c r="P170" s="13" t="str">
         <f>IF(第3日!B39="","",IFERROR(VLOOKUP(第3日!B39,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_bomber</v>
+        <v>stone_golem_elite</v>
       </c>
       <c r="Q170" s="13">
         <f>IF(第3日!B39="","",第3日!C39)</f>
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="R170" s="13">
         <v>-1</v>
@@ -14593,7 +14597,7 @@
       </c>
       <c r="I171" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J171" s="13">
         <f>第3日!G32</f>
@@ -14622,7 +14626,7 @@
       </c>
       <c r="Q171" s="13">
         <f>IF(第3日!B40="","",第3日!C40)</f>
-        <v>16</v>
+        <v>300</v>
       </c>
       <c r="R171" s="13">
         <v>-1</v>
@@ -14661,7 +14665,7 @@
       </c>
       <c r="I172" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J172" s="13">
         <f>第3日!G32</f>
@@ -14686,11 +14690,11 @@
       </c>
       <c r="P172" s="13" t="str">
         <f>IF(第3日!B41="","",IFERROR(VLOOKUP(第3日!B41,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_fire_ranged</v>
+        <v>cardboard_monster</v>
       </c>
       <c r="Q172" s="13">
         <f>IF(第3日!B41="","",第3日!C41)</f>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="R172" s="13">
         <v>-1</v>
@@ -14729,7 +14733,7 @@
       </c>
       <c r="I173" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J173" s="13">
         <f>第3日!G32</f>
@@ -14754,11 +14758,11 @@
       </c>
       <c r="P173" s="13" t="str">
         <f>IF(第3日!B42="","",IFERROR(VLOOKUP(第3日!B42,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_green_shell</v>
+        <v>combat_robot_ninja</v>
       </c>
       <c r="Q173" s="13">
         <f>IF(第3日!B42="","",第3日!C42)</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R173" s="13">
         <v>-1</v>
@@ -14797,7 +14801,7 @@
       </c>
       <c r="I174" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J174" s="13">
         <f>第3日!G32</f>
@@ -14822,11 +14826,11 @@
       </c>
       <c r="P174" s="13" t="str">
         <f>IF(第3日!B43="","",IFERROR(VLOOKUP(第3日!B43,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_guardian</v>
+        <v>combat_robot_ninja_elite</v>
       </c>
       <c r="Q174" s="13">
         <f>IF(第3日!B43="","",第3日!C43)</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R174" s="13">
         <v>-1</v>
@@ -14865,7 +14869,7 @@
       </c>
       <c r="I175" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J175" s="13">
         <f>第3日!G32</f>
@@ -14890,11 +14894,11 @@
       </c>
       <c r="P175" s="13" t="str">
         <f>IF(第3日!B44="","",IFERROR(VLOOKUP(第3日!B44,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>capoo_ak47</v>
+        <v>yuanshi_insect_guardian</v>
       </c>
       <c r="Q175" s="13">
         <f>IF(第3日!B44="","",第3日!C44)</f>
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="R175" s="13">
         <v>-1</v>
@@ -14933,7 +14937,7 @@
       </c>
       <c r="I176" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J176" s="13">
         <f>第3日!G32</f>
@@ -14958,11 +14962,11 @@
       </c>
       <c r="P176" s="13" t="str">
         <f>IF(第3日!B45="","",IFERROR(VLOOKUP(第3日!B45,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>capoo_knight</v>
+        <v>capoo_knight_elite</v>
       </c>
       <c r="Q176" s="13">
         <f>IF(第3日!B45="","",第3日!C45)</f>
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="R176" s="13">
         <v>-1</v>
@@ -15001,7 +15005,7 @@
       </c>
       <c r="I177" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J177" s="13">
         <f>第3日!G32</f>
@@ -15026,18 +15030,18 @@
       </c>
       <c r="P177" s="13" t="str">
         <f>IF(第3日!B46="","",IFERROR(VLOOKUP(第3日!B46,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q177" s="13" t="str">
+        <v>combat_robot_drone_operator_elite</v>
+      </c>
+      <c r="Q177" s="13">
         <f>IF(第3日!B46="","",第3日!C46)</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="R177" s="13">
         <v>-1</v>
       </c>
       <c r="S177" s="13" t="str">
         <f>IF(第3日!B46="","",第3日!I46)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="178" spans="1:19" ht="16.5">
@@ -15069,7 +15073,7 @@
       </c>
       <c r="I178" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J178" s="13">
         <f>第3日!G32</f>
@@ -15094,18 +15098,18 @@
       </c>
       <c r="P178" s="13" t="str">
         <f>IF(第3日!B47="","",IFERROR(VLOOKUP(第3日!B47,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q178" s="13" t="str">
+        <v>combat_robot</v>
+      </c>
+      <c r="Q178" s="13">
         <f>IF(第3日!B47="","",第3日!C47)</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="R178" s="13">
         <v>-1</v>
       </c>
       <c r="S178" s="13" t="str">
         <f>IF(第3日!B47="","",第3日!I47)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="179" spans="1:19" ht="16.5">
@@ -15137,7 +15141,7 @@
       </c>
       <c r="I179" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J179" s="13">
         <f>第3日!G32</f>
@@ -15162,18 +15166,18 @@
       </c>
       <c r="P179" s="13" t="str">
         <f>IF(第3日!B48="","",IFERROR(VLOOKUP(第3日!B48,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q179" s="13" t="str">
+        <v>combat_robot_elite</v>
+      </c>
+      <c r="Q179" s="13">
         <f>IF(第3日!B48="","",第3日!C48)</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="R179" s="13">
         <v>-1</v>
       </c>
       <c r="S179" s="13" t="str">
         <f>IF(第3日!B48="","",第3日!I48)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="180" spans="1:19" ht="16.5">
@@ -15205,7 +15209,7 @@
       </c>
       <c r="I180" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J180" s="13">
         <f>第3日!G32</f>
@@ -15230,18 +15234,18 @@
       </c>
       <c r="P180" s="13" t="str">
         <f>IF(第3日!B49="","",IFERROR(VLOOKUP(第3日!B49,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q180" s="13" t="str">
+        <v>capoo_sniper</v>
+      </c>
+      <c r="Q180" s="13">
         <f>IF(第3日!B49="","",第3日!C49)</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="R180" s="13">
         <v>-1</v>
       </c>
       <c r="S180" s="13" t="str">
         <f>IF(第3日!B49="","",第3日!I49)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="181" spans="1:19" ht="16.5">
@@ -15273,7 +15277,7 @@
       </c>
       <c r="I181" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J181" s="13">
         <f>第3日!G32</f>
@@ -15298,18 +15302,18 @@
       </c>
       <c r="P181" s="13" t="str">
         <f>IF(第3日!B50="","",IFERROR(VLOOKUP(第3日!B50,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q181" s="13" t="str">
+        <v>combat_robot_shield_bearer_elite</v>
+      </c>
+      <c r="Q181" s="13">
         <f>IF(第3日!B50="","",第3日!C50)</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="R181" s="13">
         <v>-1</v>
       </c>
       <c r="S181" s="13" t="str">
         <f>IF(第3日!B50="","",第3日!I50)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="182" spans="1:19" ht="16.5">
@@ -15341,7 +15345,7 @@
       </c>
       <c r="I182" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J182" s="13">
         <f>第3日!G32</f>
@@ -15409,7 +15413,7 @@
       </c>
       <c r="I183" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J183" s="13">
         <f>第3日!G32</f>
@@ -15477,7 +15481,7 @@
       </c>
       <c r="I184" s="13">
         <f>第3日!E32</f>
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="J184" s="13">
         <f>第3日!G32</f>
@@ -15545,7 +15549,7 @@
       </c>
       <c r="I185" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J185" s="13">
         <f>第3日!G61</f>
@@ -15570,11 +15574,11 @@
       </c>
       <c r="P185" s="13" t="str">
         <f>IF(第3日!B65="","",IFERROR(VLOOKUP(第3日!B65,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_basic</v>
+        <v>capoo_ak47</v>
       </c>
       <c r="Q185" s="13">
         <f>IF(第3日!B65="","",第3日!C65)</f>
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="R185" s="13">
         <v>-1</v>
@@ -15613,7 +15617,7 @@
       </c>
       <c r="I186" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J186" s="13">
         <f>第3日!G61</f>
@@ -15638,11 +15642,11 @@
       </c>
       <c r="P186" s="13" t="str">
         <f>IF(第3日!B66="","",IFERROR(VLOOKUP(第3日!B66,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_fast</v>
+        <v>yuanshi_insect_guardian</v>
       </c>
       <c r="Q186" s="13">
         <f>IF(第3日!B66="","",第3日!C66)</f>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="R186" s="13">
         <v>-1</v>
@@ -15681,7 +15685,7 @@
       </c>
       <c r="I187" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J187" s="13">
         <f>第3日!G61</f>
@@ -15706,11 +15710,11 @@
       </c>
       <c r="P187" s="13" t="str">
         <f>IF(第3日!B67="","",IFERROR(VLOOKUP(第3日!B67,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_shell</v>
+        <v>combat_robot_shield_bearer</v>
       </c>
       <c r="Q187" s="13">
         <f>IF(第3日!B67="","",第3日!C67)</f>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="R187" s="13">
         <v>-1</v>
@@ -15749,7 +15753,7 @@
       </c>
       <c r="I188" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J188" s="13">
         <f>第3日!G61</f>
@@ -15774,11 +15778,11 @@
       </c>
       <c r="P188" s="13" t="str">
         <f>IF(第3日!B68="","",IFERROR(VLOOKUP(第3日!B68,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_bomber</v>
+        <v>combat_robot_drone_operator</v>
       </c>
       <c r="Q188" s="13">
         <f>IF(第3日!B68="","",第3日!C68)</f>
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="R188" s="13">
         <v>-1</v>
@@ -15817,7 +15821,7 @@
       </c>
       <c r="I189" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J189" s="13">
         <f>第3日!G61</f>
@@ -15842,11 +15846,11 @@
       </c>
       <c r="P189" s="13" t="str">
         <f>IF(第3日!B69="","",IFERROR(VLOOKUP(第3日!B69,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_purple_bomber</v>
+        <v>combat_robot_gunner_elite</v>
       </c>
       <c r="Q189" s="13">
         <f>IF(第3日!B69="","",第3日!C69)</f>
-        <v>16</v>
+        <v>400</v>
       </c>
       <c r="R189" s="13">
         <v>-1</v>
@@ -15885,7 +15889,7 @@
       </c>
       <c r="I190" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J190" s="13">
         <f>第3日!G61</f>
@@ -15910,11 +15914,11 @@
       </c>
       <c r="P190" s="13" t="str">
         <f>IF(第3日!B70="","",IFERROR(VLOOKUP(第3日!B70,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_fire_ranged</v>
+        <v>stone_golem_elite</v>
       </c>
       <c r="Q190" s="13">
         <f>IF(第3日!B70="","",第3日!C70)</f>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="R190" s="13">
         <v>-1</v>
@@ -15953,7 +15957,7 @@
       </c>
       <c r="I191" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J191" s="13">
         <f>第3日!G61</f>
@@ -15978,11 +15982,11 @@
       </c>
       <c r="P191" s="13" t="str">
         <f>IF(第3日!B71="","",IFERROR(VLOOKUP(第3日!B71,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_green_shell</v>
+        <v>combat_robot_main_battle_elite</v>
       </c>
       <c r="Q191" s="13">
         <f>IF(第3日!B71="","",第3日!C71)</f>
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="R191" s="13">
         <v>-1</v>
@@ -16021,7 +16025,7 @@
       </c>
       <c r="I192" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J192" s="13">
         <f>第3日!G61</f>
@@ -16046,11 +16050,11 @@
       </c>
       <c r="P192" s="13" t="str">
         <f>IF(第3日!B72="","",IFERROR(VLOOKUP(第3日!B72,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_guardian</v>
+        <v>frost_sorcerer_elite</v>
       </c>
       <c r="Q192" s="13">
         <f>IF(第3日!B72="","",第3日!C72)</f>
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="R192" s="13">
         <v>-1</v>
@@ -16089,7 +16093,7 @@
       </c>
       <c r="I193" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J193" s="13">
         <f>第3日!G61</f>
@@ -16114,11 +16118,11 @@
       </c>
       <c r="P193" s="13" t="str">
         <f>IF(第3日!B73="","",IFERROR(VLOOKUP(第3日!B73,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>capoo_ak47</v>
+        <v>lightning_sorcerer_elite</v>
       </c>
       <c r="Q193" s="13">
         <f>IF(第3日!B73="","",第3日!C73)</f>
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="R193" s="13">
         <v>-1</v>
@@ -16157,7 +16161,7 @@
       </c>
       <c r="I194" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J194" s="13">
         <f>第3日!G61</f>
@@ -16182,11 +16186,11 @@
       </c>
       <c r="P194" s="13" t="str">
         <f>IF(第3日!B74="","",IFERROR(VLOOKUP(第3日!B74,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>capoo_knight</v>
+        <v>combat_robot_elite</v>
       </c>
       <c r="Q194" s="13">
         <f>IF(第3日!B74="","",第3日!C74)</f>
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="R194" s="13">
         <v>-1</v>
@@ -16225,7 +16229,7 @@
       </c>
       <c r="I195" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J195" s="13">
         <f>第3日!G61</f>
@@ -16250,11 +16254,11 @@
       </c>
       <c r="P195" s="13" t="str">
         <f>IF(第3日!B75="","",IFERROR(VLOOKUP(第3日!B75,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>capoo_mage</v>
+        <v>cardboard_monster</v>
       </c>
       <c r="Q195" s="13">
         <f>IF(第3日!B75="","",第3日!C75)</f>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="R195" s="13">
         <v>-1</v>
@@ -16293,7 +16297,7 @@
       </c>
       <c r="I196" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J196" s="13">
         <f>第3日!G61</f>
@@ -16318,11 +16322,11 @@
       </c>
       <c r="P196" s="13" t="str">
         <f>IF(第3日!B76="","",IFERROR(VLOOKUP(第3日!B76,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>stone_golem</v>
+        <v>combat_robot_ninja_elite</v>
       </c>
       <c r="Q196" s="13">
         <f>IF(第3日!B76="","",第3日!C76)</f>
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="R196" s="13">
         <v>-1</v>
@@ -16361,7 +16365,7 @@
       </c>
       <c r="I197" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J197" s="13">
         <f>第3日!G61</f>
@@ -16386,18 +16390,18 @@
       </c>
       <c r="P197" s="13" t="str">
         <f>IF(第3日!B77="","",IFERROR(VLOOKUP(第3日!B77,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q197" s="13" t="str">
+        <v>slime_golden</v>
+      </c>
+      <c r="Q197" s="13">
         <f>IF(第3日!B77="","",第3日!C77)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="R197" s="13">
         <v>-1</v>
       </c>
       <c r="S197" s="13" t="str">
         <f>IF(第3日!B77="","",第3日!I77)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="198" spans="1:19" ht="16.5">
@@ -16429,7 +16433,7 @@
       </c>
       <c r="I198" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J198" s="13">
         <f>第3日!G61</f>
@@ -16454,18 +16458,18 @@
       </c>
       <c r="P198" s="13" t="str">
         <f>IF(第3日!B78="","",IFERROR(VLOOKUP(第3日!B78,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q198" s="13" t="str">
+        <v>slime_fire</v>
+      </c>
+      <c r="Q198" s="13">
         <f>IF(第3日!B78="","",第3日!C78)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="R198" s="13">
         <v>-1</v>
       </c>
       <c r="S198" s="13" t="str">
         <f>IF(第3日!B78="","",第3日!I78)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="199" spans="1:19" ht="16.5">
@@ -16497,7 +16501,7 @@
       </c>
       <c r="I199" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J199" s="13">
         <f>第3日!G61</f>
@@ -16522,18 +16526,18 @@
       </c>
       <c r="P199" s="13" t="str">
         <f>IF(第3日!B79="","",IFERROR(VLOOKUP(第3日!B79,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q199" s="13" t="str">
+        <v>capoo_rpg</v>
+      </c>
+      <c r="Q199" s="13">
         <f>IF(第3日!B79="","",第3日!C79)</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="R199" s="13">
         <v>-1</v>
       </c>
       <c r="S199" s="13" t="str">
         <f>IF(第3日!B79="","",第3日!I79)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="200" spans="1:19" ht="16.5">
@@ -16565,7 +16569,7 @@
       </c>
       <c r="I200" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J200" s="13">
         <f>第3日!G61</f>
@@ -16590,18 +16594,18 @@
       </c>
       <c r="P200" s="13" t="str">
         <f>IF(第3日!B80="","",IFERROR(VLOOKUP(第3日!B80,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q200" s="13" t="str">
+        <v>fire_sorcerer_elite</v>
+      </c>
+      <c r="Q200" s="13">
         <f>IF(第3日!B80="","",第3日!C80)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="R200" s="13">
         <v>-1</v>
       </c>
       <c r="S200" s="13" t="str">
         <f>IF(第3日!B80="","",第3日!I80)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="201" spans="1:19" ht="16.5">
@@ -16633,7 +16637,7 @@
       </c>
       <c r="I201" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J201" s="13">
         <f>第3日!G61</f>
@@ -16701,7 +16705,7 @@
       </c>
       <c r="I202" s="13">
         <f>第3日!E61</f>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J202" s="13">
         <f>第3日!G61</f>
@@ -16769,7 +16773,7 @@
       </c>
       <c r="I203" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J203" s="13">
         <f>第3日!G90</f>
@@ -16794,11 +16798,11 @@
       </c>
       <c r="P203" s="13" t="str">
         <f>IF(第3日!B94="","",IFERROR(VLOOKUP(第3日!B94,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_basic</v>
+        <v>capoo_ak47</v>
       </c>
       <c r="Q203" s="13">
         <f>IF(第3日!B94="","",第3日!C94)</f>
-        <v>53</v>
+        <v>500</v>
       </c>
       <c r="R203" s="13">
         <v>-1</v>
@@ -16837,7 +16841,7 @@
       </c>
       <c r="I204" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J204" s="13">
         <f>第3日!G90</f>
@@ -16862,11 +16866,11 @@
       </c>
       <c r="P204" s="13" t="str">
         <f>IF(第3日!B95="","",IFERROR(VLOOKUP(第3日!B95,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_fast</v>
+        <v>yuanshi_insect_guardian</v>
       </c>
       <c r="Q204" s="13">
         <f>IF(第3日!B95="","",第3日!C95)</f>
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="R204" s="13">
         <v>-1</v>
@@ -16905,7 +16909,7 @@
       </c>
       <c r="I205" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J205" s="13">
         <f>第3日!G90</f>
@@ -16930,11 +16934,11 @@
       </c>
       <c r="P205" s="13" t="str">
         <f>IF(第3日!B96="","",IFERROR(VLOOKUP(第3日!B96,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_shell</v>
+        <v>combat_robot_shield_bearer_elite</v>
       </c>
       <c r="Q205" s="13">
         <f>IF(第3日!B96="","",第3日!C96)</f>
-        <v>24</v>
+        <v>400</v>
       </c>
       <c r="R205" s="13">
         <v>-1</v>
@@ -16973,7 +16977,7 @@
       </c>
       <c r="I206" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J206" s="13">
         <f>第3日!G90</f>
@@ -16998,11 +17002,11 @@
       </c>
       <c r="P206" s="13" t="str">
         <f>IF(第3日!B97="","",IFERROR(VLOOKUP(第3日!B97,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_bomber</v>
+        <v>combat_robot_drone_operator_elite</v>
       </c>
       <c r="Q206" s="13">
         <f>IF(第3日!B97="","",第3日!C97)</f>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="R206" s="13">
         <v>-1</v>
@@ -17041,7 +17045,7 @@
       </c>
       <c r="I207" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J207" s="13">
         <f>第3日!G90</f>
@@ -17066,11 +17070,11 @@
       </c>
       <c r="P207" s="13" t="str">
         <f>IF(第3日!B98="","",IFERROR(VLOOKUP(第3日!B98,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_purple_bomber</v>
+        <v>combat_robot_gunner_elite</v>
       </c>
       <c r="Q207" s="13">
         <f>IF(第3日!B98="","",第3日!C98)</f>
-        <v>16</v>
+        <v>400</v>
       </c>
       <c r="R207" s="13">
         <v>-1</v>
@@ -17109,7 +17113,7 @@
       </c>
       <c r="I208" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J208" s="13">
         <f>第3日!G90</f>
@@ -17134,11 +17138,11 @@
       </c>
       <c r="P208" s="13" t="str">
         <f>IF(第3日!B99="","",IFERROR(VLOOKUP(第3日!B99,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_fire_ranged</v>
+        <v>stone_golem_elite</v>
       </c>
       <c r="Q208" s="13">
         <f>IF(第3日!B99="","",第3日!C99)</f>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="R208" s="13">
         <v>-1</v>
@@ -17177,7 +17181,7 @@
       </c>
       <c r="I209" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J209" s="13">
         <f>第3日!G90</f>
@@ -17202,11 +17206,11 @@
       </c>
       <c r="P209" s="13" t="str">
         <f>IF(第3日!B100="","",IFERROR(VLOOKUP(第3日!B100,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_green_shell</v>
+        <v>combat_robot_main_battle_elite</v>
       </c>
       <c r="Q209" s="13">
         <f>IF(第3日!B100="","",第3日!C100)</f>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="R209" s="13">
         <v>-1</v>
@@ -17245,7 +17249,7 @@
       </c>
       <c r="I210" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J210" s="13">
         <f>第3日!G90</f>
@@ -17270,11 +17274,11 @@
       </c>
       <c r="P210" s="13" t="str">
         <f>IF(第3日!B101="","",IFERROR(VLOOKUP(第3日!B101,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>yuanshi_insect_guardian</v>
+        <v>frost_sorcerer_elite</v>
       </c>
       <c r="Q210" s="13">
         <f>IF(第3日!B101="","",第3日!C101)</f>
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="R210" s="13">
         <v>-1</v>
@@ -17313,7 +17317,7 @@
       </c>
       <c r="I211" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J211" s="13">
         <f>第3日!G90</f>
@@ -17338,11 +17342,11 @@
       </c>
       <c r="P211" s="13" t="str">
         <f>IF(第3日!B102="","",IFERROR(VLOOKUP(第3日!B102,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>capoo_ak47</v>
+        <v>lightning_sorcerer_elite</v>
       </c>
       <c r="Q211" s="13">
         <f>IF(第3日!B102="","",第3日!C102)</f>
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="R211" s="13">
         <v>-1</v>
@@ -17381,7 +17385,7 @@
       </c>
       <c r="I212" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J212" s="13">
         <f>第3日!G90</f>
@@ -17406,11 +17410,11 @@
       </c>
       <c r="P212" s="13" t="str">
         <f>IF(第3日!B103="","",IFERROR(VLOOKUP(第3日!B103,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>capoo_knight</v>
+        <v>combat_robot_elite</v>
       </c>
       <c r="Q212" s="13">
         <f>IF(第3日!B103="","",第3日!C103)</f>
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="R212" s="13">
         <v>-1</v>
@@ -17449,7 +17453,7 @@
       </c>
       <c r="I213" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J213" s="13">
         <f>第3日!G90</f>
@@ -17474,11 +17478,11 @@
       </c>
       <c r="P213" s="13" t="str">
         <f>IF(第3日!B104="","",IFERROR(VLOOKUP(第3日!B104,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>capoo_mage</v>
+        <v>cardboard_monster_large</v>
       </c>
       <c r="Q213" s="13">
         <f>IF(第3日!B104="","",第3日!C104)</f>
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="R213" s="13">
         <v>-1</v>
@@ -17517,7 +17521,7 @@
       </c>
       <c r="I214" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J214" s="13">
         <f>第3日!G90</f>
@@ -17542,11 +17546,11 @@
       </c>
       <c r="P214" s="13" t="str">
         <f>IF(第3日!B105="","",IFERROR(VLOOKUP(第3日!B105,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>capoo_rpg</v>
+        <v>combat_robot_ninja_elite</v>
       </c>
       <c r="Q214" s="13">
         <f>IF(第3日!B105="","",第3日!C105)</f>
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="R214" s="13">
         <v>-1</v>
@@ -17585,7 +17589,7 @@
       </c>
       <c r="I215" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J215" s="13">
         <f>第3日!G90</f>
@@ -17610,11 +17614,11 @@
       </c>
       <c r="P215" s="13" t="str">
         <f>IF(第3日!B106="","",IFERROR(VLOOKUP(第3日!B106,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v>stone_golem</v>
+        <v>slime_golden</v>
       </c>
       <c r="Q215" s="13">
         <f>IF(第3日!B106="","",第3日!C106)</f>
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="R215" s="13">
         <v>-1</v>
@@ -17653,7 +17657,7 @@
       </c>
       <c r="I216" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J216" s="13">
         <f>第3日!G90</f>
@@ -17678,18 +17682,18 @@
       </c>
       <c r="P216" s="13" t="str">
         <f>IF(第3日!B107="","",IFERROR(VLOOKUP(第3日!B107,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q216" s="13" t="str">
+        <v>slime_fire</v>
+      </c>
+      <c r="Q216" s="13">
         <f>IF(第3日!B107="","",第3日!C107)</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="R216" s="13">
         <v>-1</v>
       </c>
       <c r="S216" s="13" t="str">
         <f>IF(第3日!B107="","",第3日!I107)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="217" spans="1:19" ht="16.5">
@@ -17721,7 +17725,7 @@
       </c>
       <c r="I217" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J217" s="13">
         <f>第3日!G90</f>
@@ -17746,18 +17750,18 @@
       </c>
       <c r="P217" s="13" t="str">
         <f>IF(第3日!B108="","",IFERROR(VLOOKUP(第3日!B108,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q217" s="13" t="str">
+        <v>capoo_rpg</v>
+      </c>
+      <c r="Q217" s="13">
         <f>IF(第3日!B108="","",第3日!C108)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="R217" s="13">
         <v>-1</v>
       </c>
       <c r="S217" s="13" t="str">
         <f>IF(第3日!B108="","",第3日!I108)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="218" spans="1:19" ht="16.5">
@@ -17789,7 +17793,7 @@
       </c>
       <c r="I218" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J218" s="13">
         <f>第3日!G90</f>
@@ -17814,18 +17818,18 @@
       </c>
       <c r="P218" s="13" t="str">
         <f>IF(第3日!B109="","",IFERROR(VLOOKUP(第3日!B109,敌人目录!$A$6:$B$68,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="Q218" s="13" t="str">
+        <v>yuanshi_insect_purple_bomber</v>
+      </c>
+      <c r="Q218" s="13">
         <f>IF(第3日!B109="","",第3日!C109)</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="R218" s="13">
         <v>-1</v>
       </c>
       <c r="S218" s="13" t="str">
         <f>IF(第3日!B109="","",第3日!I109)</f>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="219" spans="1:19" ht="16.5">
@@ -17857,7 +17861,7 @@
       </c>
       <c r="I219" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J219" s="13">
         <f>第3日!G90</f>
@@ -17925,7 +17929,7 @@
       </c>
       <c r="I220" s="13">
         <f>第3日!E90</f>
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J220" s="13">
         <f>第3日!G90</f>
@@ -18289,19 +18293,19 @@
       <c r="C5" s="37"/>
       <c r="D5" s="37">
         <f>SUM(F9:F20)</f>
-        <v>21810</v>
+        <v>35930</v>
       </c>
       <c r="E5" s="37"/>
       <c r="F5" s="37"/>
       <c r="G5" s="37">
         <f>SUM(G9:G20)</f>
-        <v>21810</v>
+        <v>35930</v>
       </c>
       <c r="H5" s="37"/>
       <c r="I5" s="37"/>
       <c r="J5" s="37">
         <f>SUM(K9:K20)</f>
-        <v>57351</v>
+        <v>233650</v>
       </c>
       <c r="K5" s="37"/>
       <c r="L5" s="37"/>
@@ -18635,7 +18639,7 @@
       </c>
       <c r="L13" s="13">
         <f>IF(G13=0,0,MAX(0,(ROUNDUP(G13/第2日!G3,0)-1)*第2日!E3))</f>
-        <v>52.400000000000006</v>
+        <v>52.475000000000001</v>
       </c>
       <c r="M13" s="13">
         <f>第2日!I3</f>
@@ -18690,11 +18694,11 @@
       </c>
       <c r="L14" s="13">
         <f>IF(G14=0,0,MAX(0,(ROUNDUP(G14/第2日!G32,0)-1)*第2日!E32))</f>
-        <v>201.51</v>
+        <v>55.975000000000001</v>
       </c>
       <c r="M14" s="13">
         <f>第2日!I32</f>
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="N14" s="13">
         <f>IF(第2日!B33="点1·开启",1,0)+IF(第2日!C33="点2·开启",1,0)+IF(第2日!D33="点3·开启",1,0)+IF(第2日!E33="点4·开启",1,0)+IF(第2日!F33="点5·开启",1,0)+IF(第2日!G33="点6·开启",1,0)</f>
@@ -18745,11 +18749,11 @@
       </c>
       <c r="L15" s="13">
         <f>IF(G15=0,0,MAX(0,(ROUNDUP(G15/第2日!G61,0)-1)*第2日!E61))</f>
-        <v>171.92000000000002</v>
+        <v>53.725000000000001</v>
       </c>
       <c r="M15" s="13">
         <f>第2日!I61</f>
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="N15" s="13">
         <f>IF(第2日!B62="点1·开启",1,0)+IF(第2日!C62="点2·开启",1,0)+IF(第2日!D62="点3·开启",1,0)+IF(第2日!E62="点4·开启",1,0)+IF(第2日!F62="点5·开启",1,0)+IF(第2日!G62="点6·开启",1,0)</f>
@@ -18800,7 +18804,7 @@
       </c>
       <c r="L16" s="13">
         <f>IF(G16=0,0,MAX(0,(ROUNDUP(G16/第2日!G90,0)-1)*第2日!E90))</f>
-        <v>167.92499999999998</v>
+        <v>55.975000000000001</v>
       </c>
       <c r="M16" s="13">
         <f>第2日!I90</f>
@@ -18831,31 +18835,31 @@
       </c>
       <c r="F17" s="13">
         <f>SUM(第3日!C7:C24)</f>
-        <v>144</v>
+        <v>3120</v>
       </c>
       <c r="G17" s="13">
         <f>SUM(第3日!D7:D24)</f>
-        <v>144</v>
+        <v>3120</v>
       </c>
       <c r="H17" s="13">
         <f>COUNTA(第3日!B7:B24)</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I17" s="17">
         <f>SUM(第3日!F7:F24)</f>
-        <v>242</v>
+        <v>26700</v>
       </c>
       <c r="J17" s="17">
         <f>SUM(第3日!G7:G24)</f>
-        <v>242</v>
+        <v>26700</v>
       </c>
       <c r="K17" s="17">
         <f>SUM(第3日!H7:H24)</f>
-        <v>242</v>
+        <v>26700</v>
       </c>
       <c r="L17" s="13">
         <f>IF(G17=0,0,MAX(0,(ROUNDUP(G17/第3日!G3,0)-1)*第3日!E3))</f>
-        <v>40.040000000000006</v>
+        <v>249.52</v>
       </c>
       <c r="M17" s="13">
         <f>第3日!I3</f>
@@ -18886,31 +18890,31 @@
       </c>
       <c r="F18" s="13">
         <f>SUM(第3日!C36:C53)</f>
-        <v>160</v>
+        <v>3780</v>
       </c>
       <c r="G18" s="13">
         <f>SUM(第3日!D36:D53)</f>
-        <v>160</v>
+        <v>3780</v>
       </c>
       <c r="H18" s="13">
         <f>COUNTA(第3日!B36:B53)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I18" s="17">
         <f>SUM(第3日!F36:F53)</f>
-        <v>308</v>
+        <v>38800</v>
       </c>
       <c r="J18" s="17">
         <f>SUM(第3日!G36:G53)</f>
-        <v>308</v>
+        <v>38800</v>
       </c>
       <c r="K18" s="17">
         <f>SUM(第3日!H36:H53)</f>
-        <v>308</v>
+        <v>38800</v>
       </c>
       <c r="L18" s="13">
         <f>IF(G18=0,0,MAX(0,(ROUNDUP(G18/第3日!G32,0)-1)*第3日!E32))</f>
-        <v>41.34</v>
+        <v>302.32</v>
       </c>
       <c r="M18" s="13">
         <f>第3日!I32</f>
@@ -18941,31 +18945,31 @@
       </c>
       <c r="F19" s="13">
         <f>SUM(第3日!C65:C82)</f>
-        <v>176</v>
+        <v>3000</v>
       </c>
       <c r="G19" s="13">
         <f>SUM(第3日!D65:D82)</f>
-        <v>176</v>
+        <v>3000</v>
       </c>
       <c r="H19" s="13">
         <f>COUNTA(第3日!B65:B82)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I19" s="17">
         <f>SUM(第3日!F65:F82)</f>
-        <v>398</v>
+        <v>47200</v>
       </c>
       <c r="J19" s="17">
         <f>SUM(第3日!G65:G82)</f>
-        <v>398</v>
+        <v>47200</v>
       </c>
       <c r="K19" s="17">
         <f>SUM(第3日!H65:H82)</f>
-        <v>398</v>
+        <v>47200</v>
       </c>
       <c r="L19" s="13">
         <f>IF(G19=0,0,MAX(0,(ROUNDUP(G19/第3日!G61,0)-1)*第3日!E61))</f>
-        <v>42</v>
+        <v>119.96000000000001</v>
       </c>
       <c r="M19" s="13">
         <f>第3日!I61</f>
@@ -18996,31 +19000,31 @@
       </c>
       <c r="F20" s="13">
         <f>SUM(第3日!C94:C111)</f>
-        <v>200</v>
+        <v>4900</v>
       </c>
       <c r="G20" s="13">
         <f>SUM(第3日!D94:D111)</f>
-        <v>200</v>
+        <v>4900</v>
       </c>
       <c r="H20" s="13">
         <f>COUNTA(第3日!B94:B111)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I20" s="17">
         <f>SUM(第3日!F94:F111)</f>
-        <v>453</v>
+        <v>65000</v>
       </c>
       <c r="J20" s="17">
         <f>SUM(第3日!G94:G111)</f>
-        <v>453</v>
+        <v>65000</v>
       </c>
       <c r="K20" s="17">
         <f>SUM(第3日!H94:H111)</f>
-        <v>453</v>
+        <v>65000</v>
       </c>
       <c r="L20" s="13">
         <f>IF(G20=0,0,MAX(0,(ROUNDUP(G20/第3日!G90,0)-1)*第3日!E90))</f>
-        <v>43.78</v>
+        <v>122.47500000000001</v>
       </c>
       <c r="M20" s="13">
         <f>第3日!I90</f>
@@ -19146,15 +19150,15 @@
       </c>
       <c r="C28" s="13">
         <f>SUM(F17:F20)</f>
-        <v>680</v>
+        <v>14800</v>
       </c>
       <c r="D28" s="13">
         <f>SUM(G17:G20)</f>
-        <v>680</v>
+        <v>14800</v>
       </c>
       <c r="E28" s="13">
         <f>SUM(K17:K20)</f>
-        <v>1401</v>
+        <v>177700</v>
       </c>
       <c r="F28" s="13">
         <f>全局设置!F16</f>
@@ -19305,11 +19309,11 @@
       </c>
       <c r="B42" s="13">
         <f t="shared" si="0"/>
-        <v>242</v>
+        <v>26700</v>
       </c>
       <c r="C42" s="13">
         <f t="shared" si="1"/>
-        <v>242</v>
+        <v>26700</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="23.1" customHeight="1">
@@ -19318,11 +19322,11 @@
       </c>
       <c r="B43" s="13">
         <f t="shared" si="0"/>
-        <v>308</v>
+        <v>38800</v>
       </c>
       <c r="C43" s="13">
         <f t="shared" si="1"/>
-        <v>308</v>
+        <v>38800</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="23.1" customHeight="1">
@@ -19331,11 +19335,11 @@
       </c>
       <c r="B44" s="13">
         <f t="shared" si="0"/>
-        <v>398</v>
+        <v>47200</v>
       </c>
       <c r="C44" s="13">
         <f t="shared" si="1"/>
-        <v>398</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="23.1" customHeight="1">
@@ -19344,11 +19348,11 @@
       </c>
       <c r="B45" s="13">
         <f t="shared" si="0"/>
-        <v>453</v>
+        <v>65000</v>
       </c>
       <c r="C45" s="13">
         <f t="shared" si="1"/>
-        <v>453</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="23.1" customHeight="1"/>
@@ -19442,7 +19446,7 @@
       </c>
       <c r="B60" s="13">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="23.1" customHeight="1">
@@ -19451,7 +19455,7 @@
       </c>
       <c r="B61" s="13">
         <f t="shared" si="2"/>
-        <v>160</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="23.1" customHeight="1">
@@ -19460,7 +19464,7 @@
       </c>
       <c r="B62" s="13">
         <f t="shared" si="2"/>
-        <v>176</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="23.1" customHeight="1">
@@ -19469,7 +19473,7 @@
       </c>
       <c r="B63" s="13">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="23.1" customHeight="1"/>
@@ -19764,10 +19768,10 @@
       <c r="A3" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="41" t="s">
         <v>102</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -19820,17 +19824,17 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
     </row>
     <row r="6" spans="1:9" ht="21.95" customHeight="1">
       <c r="A6" s="6" t="s">
@@ -20482,14 +20486,14 @@
       <c r="C27" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="D27" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
     </row>
     <row r="28" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="29" spans="1:9" ht="21.95" customHeight="1"/>
@@ -20511,10 +20515,10 @@
       <c r="A32" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="41" t="s">
         <v>128</v>
       </c>
       <c r="D32" s="6" t="s">
@@ -20567,17 +20571,17 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A34" s="40" t="s">
+      <c r="A34" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
     </row>
     <row r="35" spans="1:9" ht="21.95" customHeight="1">
       <c r="A35" s="6" t="s">
@@ -21237,14 +21241,14 @@
       <c r="C56" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D56" s="41" t="s">
+      <c r="D56" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="41"/>
-      <c r="I56" s="41"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="40"/>
+      <c r="I56" s="40"/>
     </row>
     <row r="57" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="58" spans="1:9" ht="21.95" customHeight="1"/>
@@ -21266,10 +21270,10 @@
       <c r="A61" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B61" s="39" t="s">
+      <c r="B61" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C61" s="39" t="s">
+      <c r="C61" s="41" t="s">
         <v>132</v>
       </c>
       <c r="D61" s="19" t="s">
@@ -21322,17 +21326,17 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A63" s="40" t="s">
+      <c r="A63" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B63" s="40"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="40"/>
-      <c r="E63" s="40"/>
-      <c r="F63" s="40"/>
-      <c r="G63" s="40"/>
-      <c r="H63" s="40"/>
-      <c r="I63" s="40"/>
+      <c r="B63" s="39"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="39"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39"/>
+      <c r="I63" s="39"/>
     </row>
     <row r="64" spans="1:9" ht="21.95" customHeight="1">
       <c r="A64" s="19" t="s">
@@ -22000,14 +22004,14 @@
       <c r="C85" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D85" s="41" t="s">
+      <c r="D85" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E85" s="41"/>
-      <c r="F85" s="41"/>
-      <c r="G85" s="41"/>
-      <c r="H85" s="41"/>
-      <c r="I85" s="41"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="40"/>
+      <c r="H85" s="40"/>
+      <c r="I85" s="40"/>
     </row>
     <row r="86" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="87" spans="1:9" ht="21.95" customHeight="1"/>
@@ -22029,10 +22033,10 @@
       <c r="A90" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B90" s="39" t="s">
+      <c r="B90" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C90" s="39" t="s">
+      <c r="C90" s="41" t="s">
         <v>140</v>
       </c>
       <c r="D90" s="19" t="s">
@@ -22085,17 +22089,17 @@
       </c>
     </row>
     <row r="92" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A92" s="40" t="s">
+      <c r="A92" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B92" s="40"/>
-      <c r="C92" s="40"/>
-      <c r="D92" s="40"/>
-      <c r="E92" s="40"/>
-      <c r="F92" s="40"/>
-      <c r="G92" s="40"/>
-      <c r="H92" s="40"/>
-      <c r="I92" s="40"/>
+      <c r="B92" s="39"/>
+      <c r="C92" s="39"/>
+      <c r="D92" s="39"/>
+      <c r="E92" s="39"/>
+      <c r="F92" s="39"/>
+      <c r="G92" s="39"/>
+      <c r="H92" s="39"/>
+      <c r="I92" s="39"/>
     </row>
     <row r="93" spans="1:9" ht="21.95" customHeight="1">
       <c r="A93" s="19" t="s">
@@ -22771,17 +22775,27 @@
       <c r="C114" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D114" s="41" t="s">
+      <c r="D114" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E114" s="41"/>
-      <c r="F114" s="41"/>
-      <c r="G114" s="41"/>
-      <c r="H114" s="41"/>
-      <c r="I114" s="41"/>
+      <c r="E114" s="40"/>
+      <c r="F114" s="40"/>
+      <c r="G114" s="40"/>
+      <c r="H114" s="40"/>
+      <c r="I114" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="D56:I56"/>
+    <mergeCell ref="A60:I60"/>
     <mergeCell ref="A92:I92"/>
     <mergeCell ref="D114:I114"/>
     <mergeCell ref="B61:C61"/>
@@ -22789,63 +22803,44 @@
     <mergeCell ref="D85:I85"/>
     <mergeCell ref="A89:I89"/>
     <mergeCell ref="B90:C90"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="D56:I56"/>
-    <mergeCell ref="A60:I60"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="D27:I27"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
-  <dataValidations count="14">
-    <dataValidation type="list" sqref="B4 B91 B62 B33">
+  <dataValidations count="11">
+    <dataValidation type="list" sqref="B4 B91 B62 B33" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"点1·开启,点1·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C4 C91 C62 C33">
+    <dataValidation type="list" sqref="C4 C91 C62 C33" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"点2·开启,点2·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D4 D91 D62 D33">
+    <dataValidation type="list" sqref="D4 D91 D62 D33" xr:uid="{00000000-0002-0000-0300-000002000000}">
       <formula1>"点3·开启,点3·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E4 E91 E62 E33">
+    <dataValidation type="list" sqref="E4 E91 E62 E33" xr:uid="{00000000-0002-0000-0300-000003000000}">
       <formula1>"点4·开启,点4·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F4 F91 F62 F33">
+    <dataValidation type="list" sqref="F4 F91 F62 F33" xr:uid="{00000000-0002-0000-0300-000004000000}">
       <formula1>"点5·开启,点5·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G4 G91 G62 G33">
+    <dataValidation type="list" sqref="G4 G91 G62 G33" xr:uid="{00000000-0002-0000-0300-000005000000}">
       <formula1>"点6·开启,点6·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="whole" sqref="C7:C24 C94:C111 C65:C82 C36:C53">
+    <dataValidation type="whole" sqref="C7:C24 C94:C111 C65:C82 C36:C53" xr:uid="{00000000-0002-0000-0300-000006000000}">
       <formula1>1</formula1>
       <formula2>9999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" sqref="E3 E90 E61 E32">
+    <dataValidation type="decimal" sqref="E3 E90 E61 E32" xr:uid="{00000000-0002-0000-0300-000007000000}">
       <formula1>0.025</formula1>
       <formula2>60</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="G3 G90 G61 G32">
+    <dataValidation type="whole" sqref="G3 G90 G61 G32" xr:uid="{00000000-0002-0000-0300-000008000000}">
       <formula1>1</formula1>
       <formula2>4</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="I3 I90 I61 I32">
+    <dataValidation type="whole" sqref="I3 I90 I61 I32" xr:uid="{00000000-0002-0000-0300-000009000000}">
       <formula1>1</formula1>
       <formula2>999</formula2>
     </dataValidation>
-    <dataValidation type="list" errorStyle="stop" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B7:B24">
-      <formula1>INDIRECT("'敌人目录'!$A$6:$A$68")</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="stop" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B36:B53">
-      <formula1>INDIRECT("'敌人目录'!$A$6:$A$68")</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="stop" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B65:B82">
-      <formula1>INDIRECT("'敌人目录'!$A$6:$A$68")</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="stop" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B94:B111">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B7:B24 B94:B111 B65:B82 B36:B53" xr:uid="{00000000-0002-0000-0300-00000A000000}">
       <formula1>INDIRECT("'敌人目录'!$A$6:$A$68")</formula1>
     </dataValidation>
   </dataValidations>
@@ -22897,23 +22892,23 @@
       <c r="A3" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="41" t="s">
         <v>146</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>103</v>
       </c>
       <c r="E3" s="7">
-        <v>0.1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>104</v>
       </c>
       <c r="G3" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>49</v>
@@ -22953,17 +22948,17 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
     </row>
     <row r="6" spans="1:9" ht="21.95" customHeight="1">
       <c r="A6" s="6" t="s">
@@ -23655,14 +23650,14 @@
       <c r="C27" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="D27" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
     </row>
     <row r="28" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="29" spans="1:9" ht="21.95" customHeight="1"/>
@@ -23684,17 +23679,17 @@
       <c r="A32" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="41" t="s">
         <v>148</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>103</v>
       </c>
       <c r="E32" s="7">
-        <v>0.09</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>104</v>
@@ -23706,7 +23701,7 @@
         <v>49</v>
       </c>
       <c r="I32" s="7">
-        <v>275</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="21.95" customHeight="1">
@@ -23740,17 +23735,17 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A34" s="40" t="s">
+      <c r="A34" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
     </row>
     <row r="35" spans="1:9" ht="21.95" customHeight="1">
       <c r="A35" s="6" t="s">
@@ -24454,14 +24449,14 @@
       <c r="C56" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D56" s="41" t="s">
+      <c r="D56" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="41"/>
-      <c r="I56" s="41"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="40"/>
+      <c r="I56" s="40"/>
     </row>
     <row r="57" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="58" spans="1:9" ht="21.95" customHeight="1"/>
@@ -24483,17 +24478,17 @@
       <c r="A61" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B61" s="39" t="s">
+      <c r="B61" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="C61" s="39" t="s">
+      <c r="C61" s="41" t="s">
         <v>150</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>103</v>
       </c>
       <c r="E61" s="7">
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F61" s="19" t="s">
         <v>104</v>
@@ -24505,7 +24500,7 @@
         <v>49</v>
       </c>
       <c r="I61" s="7">
-        <v>285</v>
+        <v>300</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="21.95" customHeight="1">
@@ -24539,17 +24534,17 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A63" s="40" t="s">
+      <c r="A63" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B63" s="40"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="40"/>
-      <c r="E63" s="40"/>
-      <c r="F63" s="40"/>
-      <c r="G63" s="40"/>
-      <c r="H63" s="40"/>
-      <c r="I63" s="40"/>
+      <c r="B63" s="39"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="39"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39"/>
+      <c r="I63" s="39"/>
     </row>
     <row r="64" spans="1:9" ht="21.95" customHeight="1">
       <c r="A64" s="19" t="s">
@@ -25252,14 +25247,14 @@
       <c r="C85" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D85" s="41" t="s">
+      <c r="D85" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E85" s="41"/>
-      <c r="F85" s="41"/>
-      <c r="G85" s="41"/>
-      <c r="H85" s="41"/>
-      <c r="I85" s="41"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="40"/>
+      <c r="H85" s="40"/>
+      <c r="I85" s="40"/>
     </row>
     <row r="86" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="87" spans="1:9" ht="21.95" customHeight="1"/>
@@ -25281,17 +25276,17 @@
       <c r="A90" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B90" s="39" t="s">
+      <c r="B90" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="C90" s="39" t="s">
+      <c r="C90" s="41" t="s">
         <v>152</v>
       </c>
       <c r="D90" s="19" t="s">
         <v>103</v>
       </c>
       <c r="E90" s="7">
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F90" s="19" t="s">
         <v>104</v>
@@ -25337,17 +25332,17 @@
       </c>
     </row>
     <row r="92" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A92" s="40" t="s">
+      <c r="A92" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B92" s="40"/>
-      <c r="C92" s="40"/>
-      <c r="D92" s="40"/>
-      <c r="E92" s="40"/>
-      <c r="F92" s="40"/>
-      <c r="G92" s="40"/>
-      <c r="H92" s="40"/>
-      <c r="I92" s="40"/>
+      <c r="B92" s="39"/>
+      <c r="C92" s="39"/>
+      <c r="D92" s="39"/>
+      <c r="E92" s="39"/>
+      <c r="F92" s="39"/>
+      <c r="G92" s="39"/>
+      <c r="H92" s="39"/>
+      <c r="I92" s="39"/>
     </row>
     <row r="93" spans="1:9" ht="21.95" customHeight="1">
       <c r="A93" s="19" t="s">
@@ -26051,17 +26046,27 @@
       <c r="C114" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D114" s="41" t="s">
+      <c r="D114" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E114" s="41"/>
-      <c r="F114" s="41"/>
-      <c r="G114" s="41"/>
-      <c r="H114" s="41"/>
-      <c r="I114" s="41"/>
+      <c r="E114" s="40"/>
+      <c r="F114" s="40"/>
+      <c r="G114" s="40"/>
+      <c r="H114" s="40"/>
+      <c r="I114" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="D56:I56"/>
+    <mergeCell ref="A60:I60"/>
     <mergeCell ref="A92:I92"/>
     <mergeCell ref="D114:I114"/>
     <mergeCell ref="B61:C61"/>
@@ -26069,63 +26074,44 @@
     <mergeCell ref="D85:I85"/>
     <mergeCell ref="A89:I89"/>
     <mergeCell ref="B90:C90"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="D56:I56"/>
-    <mergeCell ref="A60:I60"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="D27:I27"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
-  <dataValidations count="14">
-    <dataValidation type="list" sqref="B4 B91 B62 B33">
+  <dataValidations count="11">
+    <dataValidation type="list" sqref="B4 B91 B62 B33" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"点1·开启,点1·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C4 C91 C62 C33">
+    <dataValidation type="list" sqref="C4 C91 C62 C33" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>"点2·开启,点2·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D4 D91 D62 D33">
+    <dataValidation type="list" sqref="D4 D91 D62 D33" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>"点3·开启,点3·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E4 E91 E62 E33">
+    <dataValidation type="list" sqref="E4 E91 E62 E33" xr:uid="{00000000-0002-0000-0400-000003000000}">
       <formula1>"点4·开启,点4·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F4 F91 F62 F33">
+    <dataValidation type="list" sqref="F4 F91 F62 F33" xr:uid="{00000000-0002-0000-0400-000004000000}">
       <formula1>"点5·开启,点5·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G4 G91 G62 G33">
+    <dataValidation type="list" sqref="G4 G91 G62 G33" xr:uid="{00000000-0002-0000-0400-000005000000}">
       <formula1>"点6·开启,点6·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="whole" sqref="C7:C24 C94:C111 C65:C82 C36:C53">
+    <dataValidation type="whole" sqref="C7:C24 C94:C111 C65:C82 C36:C53" xr:uid="{00000000-0002-0000-0400-000006000000}">
       <formula1>1</formula1>
       <formula2>9999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" sqref="E3 E90 E61 E32">
+    <dataValidation type="decimal" sqref="E3 E61 E32 E90" xr:uid="{00000000-0002-0000-0400-000007000000}">
       <formula1>0.025</formula1>
       <formula2>60</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="G3 G90 G61 G32">
+    <dataValidation type="whole" sqref="G3 G90 G61 G32" xr:uid="{00000000-0002-0000-0400-000008000000}">
       <formula1>1</formula1>
       <formula2>4</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="I3 I90 I61 I32">
+    <dataValidation type="whole" sqref="I3 I90 I61 I32" xr:uid="{00000000-0002-0000-0400-000009000000}">
       <formula1>1</formula1>
       <formula2>999</formula2>
     </dataValidation>
-    <dataValidation type="list" errorStyle="stop" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B7:B24">
-      <formula1>INDIRECT("'敌人目录'!$A$6:$A$68")</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="stop" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B36:B53">
-      <formula1>INDIRECT("'敌人目录'!$A$6:$A$68")</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="stop" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B65:B82">
-      <formula1>INDIRECT("'敌人目录'!$A$6:$A$68")</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="stop" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B94:B111">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B7:B24 B94:B111 B65:B82 B36:B53" xr:uid="{00000000-0002-0000-0400-00000A000000}">
       <formula1>INDIRECT("'敌人目录'!$A$6:$A$68")</formula1>
     </dataValidation>
   </dataValidations>
@@ -26177,17 +26163,17 @@
       <c r="A3" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="41" t="s">
         <v>154</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>103</v>
       </c>
       <c r="E3" s="7">
-        <v>0.28000000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>104</v>
@@ -26233,17 +26219,17 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
     </row>
     <row r="6" spans="1:9" ht="21.95" customHeight="1">
       <c r="A6" s="6" t="s">
@@ -26279,14 +26265,14 @@
         <v>1</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C7" s="14">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="D7" s="8">
         <f>IF(B7="",0,ROUNDUP(C7*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="E7" s="17">
         <f>IF(B7="",0,IFERROR(VLOOKUP(B7,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
@@ -26294,15 +26280,15 @@
       </c>
       <c r="F7" s="17">
         <f t="shared" ref="F7:F24" si="0">D7*E7</f>
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="G7" s="17">
         <f>F7*全局设置!$B$7</f>
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="H7" s="17">
         <f>G7*全局设置!$B$5</f>
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="I7" s="15" t="str">
         <f t="shared" ref="I7:I24" si="1">IF(AND(B7="",C7=""),"",IF(AND(B7&lt;&gt;"",C7&gt;=1,COUNTIF($B$7:$B$24,B7)=1),"可回读","需修正"))</f>
@@ -26314,30 +26300,30 @@
         <v>2</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="C8" s="14">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D8" s="8">
         <f>IF(B8="",0,ROUNDUP(C8*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E8" s="17">
         <f>IF(B8="",0,IFERROR(VLOOKUP(B8,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F8" s="17">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>4000</v>
       </c>
       <c r="G8" s="17">
         <f>F8*全局设置!$B$7</f>
-        <v>20</v>
+        <v>4000</v>
       </c>
       <c r="H8" s="17">
         <f>G8*全局设置!$B$5</f>
-        <v>20</v>
+        <v>4000</v>
       </c>
       <c r="I8" s="15" t="str">
         <f t="shared" si="1"/>
@@ -26349,7 +26335,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="C9" s="14">
         <v>20</v>
@@ -26360,19 +26346,19 @@
       </c>
       <c r="E9" s="17">
         <f>IF(B9="",0,IFERROR(VLOOKUP(B9,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F9" s="17">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="G9" s="17">
         <f>F9*全局设置!$B$7</f>
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="H9" s="17">
         <f>G9*全局设置!$B$5</f>
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="I9" s="15" t="str">
         <f t="shared" si="1"/>
@@ -26384,30 +26370,30 @@
         <v>4</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>136</v>
+        <v>421</v>
       </c>
       <c r="C10" s="14">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D10" s="8">
         <f>IF(B10="",0,ROUNDUP(C10*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="E10" s="17">
         <f>IF(B10="",0,IFERROR(VLOOKUP(B10,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F10" s="17">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>5000</v>
       </c>
       <c r="G10" s="17">
         <f>F10*全局设置!$B$7</f>
-        <v>16</v>
+        <v>5000</v>
       </c>
       <c r="H10" s="17">
         <f>G10*全局设置!$B$5</f>
-        <v>16</v>
+        <v>5000</v>
       </c>
       <c r="I10" s="15" t="str">
         <f t="shared" si="1"/>
@@ -26419,30 +26405,30 @@
         <v>5</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C11" s="14">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="D11" s="8">
         <f>IF(B11="",0,ROUNDUP(C11*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="E11" s="17">
         <f>IF(B11="",0,IFERROR(VLOOKUP(B11,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="17">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="G11" s="17">
         <f>F11*全局设置!$B$7</f>
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="H11" s="17">
         <f>G11*全局设置!$B$5</f>
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="I11" s="15" t="str">
         <f t="shared" si="1"/>
@@ -26454,30 +26440,30 @@
         <v>6</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>122</v>
+        <v>425</v>
       </c>
       <c r="C12" s="14">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="D12" s="8">
         <f>IF(B12="",0,ROUNDUP(C12*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="E12" s="17">
         <f>IF(B12="",0,IFERROR(VLOOKUP(B12,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="17">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="G12" s="17">
         <f>F12*全局设置!$B$7</f>
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="H12" s="17">
         <f>G12*全局设置!$B$5</f>
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="I12" s="15" t="str">
         <f t="shared" si="1"/>
@@ -26489,30 +26475,30 @@
         <v>7</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>141</v>
+        <v>467</v>
       </c>
       <c r="C13" s="14">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D13" s="8">
         <f>IF(B13="",0,ROUNDUP(C13*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E13" s="17">
         <f>IF(B13="",0,IFERROR(VLOOKUP(B13,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F13" s="17">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="G13" s="17">
         <f>F13*全局设置!$B$7</f>
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="H13" s="17">
         <f>G13*全局设置!$B$5</f>
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="I13" s="15" t="str">
         <f t="shared" si="1"/>
@@ -26524,30 +26510,30 @@
         <v>8</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>135</v>
+        <v>471</v>
       </c>
       <c r="C14" s="14">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D14" s="8">
         <f>IF(B14="",0,ROUNDUP(C14*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="E14" s="17">
         <f>IF(B14="",0,IFERROR(VLOOKUP(B14,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F14" s="17">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="G14" s="17">
         <f>F14*全局设置!$B$7</f>
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="H14" s="17">
         <f>G14*全局设置!$B$5</f>
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="I14" s="15" t="str">
         <f t="shared" si="1"/>
@@ -26559,30 +26545,30 @@
         <v>9</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D15" s="8">
         <f>IF(B15="",0,ROUNDUP(C15*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E15" s="17">
         <f>IF(B15="",0,IFERROR(VLOOKUP(B15,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="G15" s="17">
         <f>F15*全局设置!$B$7</f>
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="H15" s="17">
         <f>G15*全局设置!$B$5</f>
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="I15" s="15" t="str">
         <f t="shared" si="1"/>
@@ -26593,124 +26579,140 @@
       <c r="A16" s="16">
         <v>10</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
+      <c r="B16" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="C16" s="14">
+        <v>400</v>
+      </c>
       <c r="D16" s="8">
         <f>IF(B16="",0,ROUNDUP(C16*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E16" s="17">
         <f>IF(B16="",0,IFERROR(VLOOKUP(B16,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F16" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G16" s="17">
         <f>F16*全局设置!$B$7</f>
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="H16" s="17">
         <f>G16*全局设置!$B$5</f>
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="I16" s="15" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="21.95" customHeight="1">
       <c r="A17" s="16">
         <v>11</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
+      <c r="B17" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="C17" s="14">
+        <v>200</v>
+      </c>
       <c r="D17" s="8">
         <f>IF(B17="",0,ROUNDUP(C17*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E17" s="17">
         <f>IF(B17="",0,IFERROR(VLOOKUP(B17,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F17" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G17" s="17">
         <f>F17*全局设置!$B$7</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H17" s="17">
         <f>G17*全局设置!$B$5</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I17" s="15" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="21.95" customHeight="1">
       <c r="A18" s="16">
         <v>12</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
+      <c r="B18" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="C18" s="14">
+        <v>200</v>
+      </c>
       <c r="D18" s="8">
         <f>IF(B18="",0,ROUNDUP(C18*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E18" s="17">
         <f>IF(B18="",0,IFERROR(VLOOKUP(B18,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F18" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G18" s="17">
         <f>F18*全局设置!$B$7</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H18" s="17">
         <f>G18*全局设置!$B$5</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I18" s="15" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="21.95" customHeight="1">
       <c r="A19" s="16">
         <v>13</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
+      <c r="B19" s="14" t="s">
+        <v>570</v>
+      </c>
+      <c r="C19" s="14">
+        <v>100</v>
+      </c>
       <c r="D19" s="8">
         <f>IF(B19="",0,ROUNDUP(C19*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19" s="17">
         <f>IF(B19="",0,IFERROR(VLOOKUP(B19,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F19" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G19" s="17">
         <f>F19*全局设置!$B$7</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H19" s="17">
         <f>G19*全局设置!$B$5</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I19" s="15" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="21.95" customHeight="1">
@@ -26875,28 +26877,28 @@
       </c>
       <c r="B26" s="8">
         <f>SUM(C7:C24)</f>
-        <v>144</v>
+        <v>3120</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>124</v>
       </c>
       <c r="D26" s="8">
         <f>SUM(D7:D24)</f>
-        <v>144</v>
+        <v>3120</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>46</v>
       </c>
       <c r="F26" s="8">
         <f>SUM(F7:F24)</f>
-        <v>242</v>
+        <v>26700</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H26" s="8">
         <f>SUM(G7:G24)</f>
-        <v>242</v>
+        <v>26700</v>
       </c>
       <c r="I26" s="8"/>
     </row>
@@ -26906,19 +26908,19 @@
       </c>
       <c r="B27" s="4">
         <f>SUM(H7:H24)</f>
-        <v>242</v>
+        <v>26700</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="D27" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
     </row>
     <row r="28" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="29" spans="1:9" ht="21.95" customHeight="1"/>
@@ -26940,17 +26942,17 @@
       <c r="A32" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="41" t="s">
         <v>157</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>103</v>
       </c>
       <c r="E32" s="7">
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>104</v>
@@ -26996,17 +26998,17 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A34" s="40" t="s">
+      <c r="A34" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
     </row>
     <row r="35" spans="1:9" ht="21.95" customHeight="1">
       <c r="A35" s="6" t="s">
@@ -27042,14 +27044,14 @@
         <v>1</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C36" s="14">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="D36" s="8">
         <f>IF(B36="",0,ROUNDUP(C36*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="E36" s="17">
         <f>IF(B36="",0,IFERROR(VLOOKUP(B36,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
@@ -27057,15 +27059,15 @@
       </c>
       <c r="F36" s="17">
         <f t="shared" ref="F36:F53" si="2">D36*E36</f>
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="G36" s="17">
         <f>F36*全局设置!$B$7</f>
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="H36" s="17">
         <f>G36*全局设置!$B$5</f>
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="I36" s="15" t="str">
         <f t="shared" ref="I36:I53" si="3">IF(AND(B36="",C36=""),"",IF(AND(B36&lt;&gt;"",C36&gt;=1,COUNTIF($B$36:$B$53,B36)=1),"可回读","需修正"))</f>
@@ -27077,30 +27079,30 @@
         <v>2</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="C37" s="14">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="D37" s="8">
         <f>IF(B37="",0,ROUNDUP(C37*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="E37" s="17">
         <f>IF(B37="",0,IFERROR(VLOOKUP(B37,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F37" s="17">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>2400</v>
       </c>
       <c r="G37" s="17">
         <f>F37*全局设置!$B$7</f>
-        <v>24</v>
+        <v>2400</v>
       </c>
       <c r="H37" s="17">
         <f>G37*全局设置!$B$5</f>
-        <v>24</v>
+        <v>2400</v>
       </c>
       <c r="I37" s="15" t="str">
         <f t="shared" si="3"/>
@@ -27112,30 +27114,30 @@
         <v>3</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="C38" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D38" s="8">
         <f>IF(B38="",0,ROUNDUP(C38*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E38" s="17">
         <f>IF(B38="",0,IFERROR(VLOOKUP(B38,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F38" s="17">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="G38" s="17">
         <f>F38*全局设置!$B$7</f>
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="H38" s="17">
         <f>G38*全局设置!$B$5</f>
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="I38" s="15" t="str">
         <f t="shared" si="3"/>
@@ -27147,30 +27149,30 @@
         <v>4</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>136</v>
+        <v>421</v>
       </c>
       <c r="C39" s="14">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D39" s="8">
         <f>IF(B39="",0,ROUNDUP(C39*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="E39" s="17">
         <f>IF(B39="",0,IFERROR(VLOOKUP(B39,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F39" s="17">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>6000</v>
       </c>
       <c r="G39" s="17">
         <f>F39*全局设置!$B$7</f>
-        <v>20</v>
+        <v>6000</v>
       </c>
       <c r="H39" s="17">
         <f>G39*全局设置!$B$5</f>
-        <v>20</v>
+        <v>6000</v>
       </c>
       <c r="I39" s="15" t="str">
         <f t="shared" si="3"/>
@@ -27185,11 +27187,11 @@
         <v>138</v>
       </c>
       <c r="C40" s="14">
-        <v>16</v>
+        <v>300</v>
       </c>
       <c r="D40" s="8">
         <f>IF(B40="",0,ROUNDUP(C40*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>16</v>
+        <v>300</v>
       </c>
       <c r="E40" s="17">
         <f>IF(B40="",0,IFERROR(VLOOKUP(B40,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
@@ -27197,15 +27199,15 @@
       </c>
       <c r="F40" s="17">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>600</v>
       </c>
       <c r="G40" s="17">
         <f>F40*全局设置!$B$7</f>
-        <v>32</v>
+        <v>600</v>
       </c>
       <c r="H40" s="17">
         <f>G40*全局设置!$B$5</f>
-        <v>32</v>
+        <v>600</v>
       </c>
       <c r="I40" s="15" t="str">
         <f t="shared" si="3"/>
@@ -27217,30 +27219,30 @@
         <v>6</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>122</v>
+        <v>425</v>
       </c>
       <c r="C41" s="14">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="D41" s="8">
         <f>IF(B41="",0,ROUNDUP(C41*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="E41" s="17">
         <f>IF(B41="",0,IFERROR(VLOOKUP(B41,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="17">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="G41" s="17">
         <f>F41*全局设置!$B$7</f>
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="H41" s="17">
         <f>G41*全局设置!$B$5</f>
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="I41" s="15" t="str">
         <f t="shared" si="3"/>
@@ -27252,30 +27254,30 @@
         <v>7</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>141</v>
+        <v>467</v>
       </c>
       <c r="C42" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D42" s="8">
         <f>IF(B42="",0,ROUNDUP(C42*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E42" s="17">
         <f>IF(B42="",0,IFERROR(VLOOKUP(B42,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F42" s="17">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="G42" s="17">
         <f>F42*全局设置!$B$7</f>
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="H42" s="17">
         <f>G42*全局设置!$B$5</f>
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="I42" s="15" t="str">
         <f t="shared" si="3"/>
@@ -27287,30 +27289,30 @@
         <v>8</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>135</v>
+        <v>471</v>
       </c>
       <c r="C43" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D43" s="8">
         <f>IF(B43="",0,ROUNDUP(C43*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E43" s="17">
         <f>IF(B43="",0,IFERROR(VLOOKUP(B43,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="G43" s="17">
         <f>F43*全局设置!$B$7</f>
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="H43" s="17">
         <f>G43*全局设置!$B$5</f>
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="I43" s="15" t="str">
         <f t="shared" si="3"/>
@@ -27322,30 +27324,30 @@
         <v>9</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C44" s="14">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D44" s="8">
         <f>IF(B44="",0,ROUNDUP(C44*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E44" s="17">
         <f>IF(B44="",0,IFERROR(VLOOKUP(B44,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" si="2"/>
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="G44" s="17">
         <f>F44*全局设置!$B$7</f>
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="H44" s="17">
         <f>G44*全局设置!$B$5</f>
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="I44" s="15" t="str">
         <f t="shared" si="3"/>
@@ -27357,14 +27359,14 @@
         <v>10</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>155</v>
+        <v>332</v>
       </c>
       <c r="C45" s="14">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="D45" s="8">
         <f>IF(B45="",0,ROUNDUP(C45*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="E45" s="17">
         <f>IF(B45="",0,IFERROR(VLOOKUP(B45,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
@@ -27372,15 +27374,15 @@
       </c>
       <c r="F45" s="17">
         <f t="shared" si="2"/>
-        <v>40</v>
+        <v>8000</v>
       </c>
       <c r="G45" s="17">
         <f>F45*全局设置!$B$7</f>
-        <v>40</v>
+        <v>8000</v>
       </c>
       <c r="H45" s="17">
         <f>G45*全局设置!$B$5</f>
-        <v>40</v>
+        <v>8000</v>
       </c>
       <c r="I45" s="15" t="str">
         <f t="shared" si="3"/>
@@ -27391,155 +27393,175 @@
       <c r="A46" s="16">
         <v>11</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
+      <c r="B46" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="C46" s="14">
+        <v>200</v>
+      </c>
       <c r="D46" s="8">
         <f>IF(B46="",0,ROUNDUP(C46*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E46" s="17">
         <f>IF(B46="",0,IFERROR(VLOOKUP(B46,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F46" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G46" s="17">
         <f>F46*全局设置!$B$7</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H46" s="17">
         <f>G46*全局设置!$B$5</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I46" s="15" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="21.95" customHeight="1">
       <c r="A47" s="16">
         <v>12</v>
       </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
+      <c r="B47" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="C47" s="14">
+        <v>200</v>
+      </c>
       <c r="D47" s="8">
         <f>IF(B47="",0,ROUNDUP(C47*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E47" s="17">
         <f>IF(B47="",0,IFERROR(VLOOKUP(B47,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F47" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G47" s="17">
         <f>F47*全局设置!$B$7</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H47" s="17">
         <f>G47*全局设置!$B$5</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I47" s="15" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="21.95" customHeight="1">
       <c r="A48" s="16">
         <v>13</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
+      <c r="B48" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="C48" s="14">
+        <v>500</v>
+      </c>
       <c r="D48" s="8">
         <f>IF(B48="",0,ROUNDUP(C48*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E48" s="17">
         <f>IF(B48="",0,IFERROR(VLOOKUP(B48,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F48" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G48" s="17">
         <f>F48*全局设置!$B$7</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H48" s="17">
         <f>G48*全局设置!$B$5</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I48" s="15" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="21.95" customHeight="1">
       <c r="A49" s="16">
         <v>14</v>
       </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
+      <c r="B49" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="C49" s="14">
+        <v>200</v>
+      </c>
       <c r="D49" s="8">
         <f>IF(B49="",0,ROUNDUP(C49*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E49" s="17">
         <f>IF(B49="",0,IFERROR(VLOOKUP(B49,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F49" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G49" s="17">
         <f>F49*全局设置!$B$7</f>
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H49" s="17">
         <f>G49*全局设置!$B$5</f>
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="I49" s="15" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="21.95" customHeight="1">
       <c r="A50" s="16">
         <v>15</v>
       </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
+      <c r="B50" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="C50" s="14">
+        <v>200</v>
+      </c>
       <c r="D50" s="8">
         <f>IF(B50="",0,ROUNDUP(C50*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E50" s="17">
         <f>IF(B50="",0,IFERROR(VLOOKUP(B50,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F50" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G50" s="17">
         <f>F50*全局设置!$B$7</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H50" s="17">
         <f>G50*全局设置!$B$5</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I50" s="15" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="21.95" customHeight="1">
@@ -27642,28 +27664,28 @@
       </c>
       <c r="B55" s="8">
         <f>SUM(C36:C53)</f>
-        <v>160</v>
+        <v>3780</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>124</v>
       </c>
       <c r="D55" s="8">
         <f>SUM(D36:D53)</f>
-        <v>160</v>
+        <v>3780</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>46</v>
       </c>
       <c r="F55" s="8">
         <f>SUM(F36:F53)</f>
-        <v>308</v>
+        <v>38800</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H55" s="8">
         <f>SUM(G36:G53)</f>
-        <v>308</v>
+        <v>38800</v>
       </c>
       <c r="I55" s="8"/>
     </row>
@@ -27673,19 +27695,19 @@
       </c>
       <c r="B56" s="4">
         <f>SUM(H36:H53)</f>
-        <v>308</v>
+        <v>38800</v>
       </c>
       <c r="C56" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D56" s="41" t="s">
+      <c r="D56" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="41"/>
-      <c r="I56" s="41"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="40"/>
+      <c r="I56" s="40"/>
     </row>
     <row r="57" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="58" spans="1:9" ht="21.95" customHeight="1"/>
@@ -27707,17 +27729,17 @@
       <c r="A61" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B61" s="39" t="s">
+      <c r="B61" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="C61" s="39" t="s">
+      <c r="C61" s="41" t="s">
         <v>159</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>103</v>
       </c>
       <c r="E61" s="7">
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="F61" s="19" t="s">
         <v>104</v>
@@ -27763,17 +27785,17 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A63" s="40" t="s">
+      <c r="A63" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B63" s="40"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="40"/>
-      <c r="E63" s="40"/>
-      <c r="F63" s="40"/>
-      <c r="G63" s="40"/>
-      <c r="H63" s="40"/>
-      <c r="I63" s="40"/>
+      <c r="B63" s="39"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="39"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39"/>
+      <c r="I63" s="39"/>
     </row>
     <row r="64" spans="1:9" ht="21.95" customHeight="1">
       <c r="A64" s="19" t="s">
@@ -27809,30 +27831,30 @@
         <v>1</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="C65" s="14">
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="D65" s="8">
         <f>IF(B65="",0,ROUNDUP(C65*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="E65" s="17">
         <f>IF(B65="",0,IFERROR(VLOOKUP(B65,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F65" s="17">
         <f t="shared" ref="F65:F82" si="4">D65*E65</f>
-        <v>46</v>
+        <v>4000</v>
       </c>
       <c r="G65" s="17">
         <f>F65*全局设置!$B$7</f>
-        <v>46</v>
+        <v>4000</v>
       </c>
       <c r="H65" s="17">
         <f>G65*全局设置!$B$5</f>
-        <v>46</v>
+        <v>4000</v>
       </c>
       <c r="I65" s="15" t="str">
         <f t="shared" ref="I65:I82" si="5">IF(AND(B65="",C65=""),"",IF(AND(B65&lt;&gt;"",C65&gt;=1,COUNTIF($B$65:$B$82,B65)=1),"可回读","需修正"))</f>
@@ -27844,30 +27866,30 @@
         <v>2</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C66" s="14">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D66" s="8">
         <f>IF(B66="",0,ROUNDUP(C66*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E66" s="17">
         <f>IF(B66="",0,IFERROR(VLOOKUP(B66,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="17">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="G66" s="17">
         <f>F66*全局设置!$B$7</f>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="H66" s="17">
         <f>G66*全局设置!$B$5</f>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="I66" s="15" t="str">
         <f t="shared" si="5"/>
@@ -27879,30 +27901,30 @@
         <v>3</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>129</v>
+        <v>459</v>
       </c>
       <c r="C67" s="14">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="D67" s="8">
         <f>IF(B67="",0,ROUNDUP(C67*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="E67" s="17">
         <f>IF(B67="",0,IFERROR(VLOOKUP(B67,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F67" s="17">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>4000</v>
       </c>
       <c r="G67" s="17">
         <f>F67*全局设置!$B$7</f>
-        <v>40</v>
+        <v>4000</v>
       </c>
       <c r="H67" s="17">
         <f>G67*全局设置!$B$5</f>
-        <v>40</v>
+        <v>4000</v>
       </c>
       <c r="I67" s="15" t="str">
         <f t="shared" si="5"/>
@@ -27914,30 +27936,30 @@
         <v>4</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>136</v>
+        <v>451</v>
       </c>
       <c r="C68" s="14">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="D68" s="8">
         <f>IF(B68="",0,ROUNDUP(C68*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="E68" s="17">
         <f>IF(B68="",0,IFERROR(VLOOKUP(B68,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F68" s="17">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>2000</v>
       </c>
       <c r="G68" s="17">
         <f>F68*全局设置!$B$7</f>
-        <v>16</v>
+        <v>2000</v>
       </c>
       <c r="H68" s="17">
         <f>G68*全局设置!$B$5</f>
-        <v>16</v>
+        <v>2000</v>
       </c>
       <c r="I68" s="15" t="str">
         <f t="shared" si="5"/>
@@ -27949,30 +27971,30 @@
         <v>5</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>138</v>
+        <v>447</v>
       </c>
       <c r="C69" s="14">
-        <v>16</v>
+        <v>400</v>
       </c>
       <c r="D69" s="8">
         <f>IF(B69="",0,ROUNDUP(C69*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>16</v>
+        <v>400</v>
       </c>
       <c r="E69" s="17">
         <f>IF(B69="",0,IFERROR(VLOOKUP(B69,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F69" s="17">
         <f t="shared" si="4"/>
-        <v>32</v>
+        <v>4000</v>
       </c>
       <c r="G69" s="17">
         <f>F69*全局设置!$B$7</f>
-        <v>32</v>
+        <v>4000</v>
       </c>
       <c r="H69" s="17">
         <f>G69*全局设置!$B$5</f>
-        <v>32</v>
+        <v>4000</v>
       </c>
       <c r="I69" s="15" t="str">
         <f t="shared" si="5"/>
@@ -27984,30 +28006,30 @@
         <v>6</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>122</v>
+        <v>421</v>
       </c>
       <c r="C70" s="14">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D70" s="8">
         <f>IF(B70="",0,ROUNDUP(C70*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E70" s="17">
         <f>IF(B70="",0,IFERROR(VLOOKUP(B70,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F70" s="17">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>5000</v>
       </c>
       <c r="G70" s="17">
         <f>F70*全局设置!$B$7</f>
-        <v>20</v>
+        <v>5000</v>
       </c>
       <c r="H70" s="17">
         <f>G70*全局设置!$B$5</f>
-        <v>20</v>
+        <v>5000</v>
       </c>
       <c r="I70" s="15" t="str">
         <f t="shared" si="5"/>
@@ -28019,30 +28041,30 @@
         <v>7</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>141</v>
+        <v>475</v>
       </c>
       <c r="C71" s="14">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D71" s="8">
         <f>IF(B71="",0,ROUNDUP(C71*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="E71" s="17">
         <f>IF(B71="",0,IFERROR(VLOOKUP(B71,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F71" s="17">
         <f t="shared" si="4"/>
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="G71" s="17">
         <f>F71*全局设置!$B$7</f>
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="H71" s="17">
         <f>G71*全局设置!$B$5</f>
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="I71" s="15" t="str">
         <f t="shared" si="5"/>
@@ -28054,30 +28076,30 @@
         <v>8</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>135</v>
+        <v>404</v>
       </c>
       <c r="C72" s="14">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="D72" s="8">
         <f>IF(B72="",0,ROUNDUP(C72*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="E72" s="17">
         <f>IF(B72="",0,IFERROR(VLOOKUP(B72,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="F72" s="17">
         <f t="shared" si="4"/>
-        <v>32</v>
+        <v>7000</v>
       </c>
       <c r="G72" s="17">
         <f>F72*全局设置!$B$7</f>
-        <v>32</v>
+        <v>7000</v>
       </c>
       <c r="H72" s="17">
         <f>G72*全局设置!$B$5</f>
-        <v>32</v>
+        <v>7000</v>
       </c>
       <c r="I72" s="15" t="str">
         <f t="shared" si="5"/>
@@ -28089,30 +28111,30 @@
         <v>9</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>144</v>
+        <v>412</v>
       </c>
       <c r="C73" s="14">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D73" s="8">
         <f>IF(B73="",0,ROUNDUP(C73*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="E73" s="17">
         <f>IF(B73="",0,IFERROR(VLOOKUP(B73,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F73" s="17">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>7000</v>
       </c>
       <c r="G73" s="17">
         <f>F73*全局设置!$B$7</f>
-        <v>40</v>
+        <v>7000</v>
       </c>
       <c r="H73" s="17">
         <f>G73*全局设置!$B$5</f>
-        <v>40</v>
+        <v>7000</v>
       </c>
       <c r="I73" s="15" t="str">
         <f t="shared" si="5"/>
@@ -28124,30 +28146,30 @@
         <v>10</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>155</v>
+        <v>439</v>
       </c>
       <c r="C74" s="14">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D74" s="8">
         <f>IF(B74="",0,ROUNDUP(C74*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="E74" s="17">
         <f>IF(B74="",0,IFERROR(VLOOKUP(B74,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F74" s="17">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>2000</v>
       </c>
       <c r="G74" s="17">
         <f>F74*全局设置!$B$7</f>
-        <v>40</v>
+        <v>2000</v>
       </c>
       <c r="H74" s="17">
         <f>G74*全局设置!$B$5</f>
-        <v>40</v>
+        <v>2000</v>
       </c>
       <c r="I74" s="15" t="str">
         <f t="shared" si="5"/>
@@ -28159,30 +28181,30 @@
         <v>11</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>160</v>
+        <v>425</v>
       </c>
       <c r="C75" s="14">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D75" s="8">
         <f>IF(B75="",0,ROUNDUP(C75*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E75" s="17">
         <f>IF(B75="",0,IFERROR(VLOOKUP(B75,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F75" s="17">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="G75" s="17">
         <f>F75*全局设置!$B$7</f>
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="H75" s="17">
         <f>G75*全局设置!$B$5</f>
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I75" s="15" t="str">
         <f t="shared" si="5"/>
@@ -28194,30 +28216,30 @@
         <v>12</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>161</v>
+        <v>471</v>
       </c>
       <c r="C76" s="14">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D76" s="8">
         <f>IF(B76="",0,ROUNDUP(C76*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="E76" s="17">
         <f>IF(B76="",0,IFERROR(VLOOKUP(B76,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F76" s="17">
         <f t="shared" si="4"/>
-        <v>50</v>
+        <v>2000</v>
       </c>
       <c r="G76" s="17">
         <f>F76*全局设置!$B$7</f>
-        <v>50</v>
+        <v>2000</v>
       </c>
       <c r="H76" s="17">
         <f>G76*全局设置!$B$5</f>
-        <v>50</v>
+        <v>2000</v>
       </c>
       <c r="I76" s="15" t="str">
         <f t="shared" si="5"/>
@@ -28228,124 +28250,140 @@
       <c r="A77" s="16">
         <v>13</v>
       </c>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
+      <c r="B77" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C77" s="14">
+        <v>100</v>
+      </c>
       <c r="D77" s="8">
         <f>IF(B77="",0,ROUNDUP(C77*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E77" s="17">
         <f>IF(B77="",0,IFERROR(VLOOKUP(B77,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="17">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G77" s="17">
         <f>F77*全局设置!$B$7</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H77" s="17">
         <f>G77*全局设置!$B$5</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I77" s="15" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="21.95" customHeight="1">
       <c r="A78" s="16">
         <v>14</v>
       </c>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
+      <c r="B78" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C78" s="14">
+        <v>100</v>
+      </c>
       <c r="D78" s="8">
         <f>IF(B78="",0,ROUNDUP(C78*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E78" s="17">
         <f>IF(B78="",0,IFERROR(VLOOKUP(B78,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="17">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G78" s="17">
         <f>F78*全局设置!$B$7</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H78" s="17">
         <f>G78*全局设置!$B$5</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I78" s="15" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="21.95" customHeight="1">
       <c r="A79" s="16">
         <v>15</v>
       </c>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
+      <c r="B79" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C79" s="14">
+        <v>200</v>
+      </c>
       <c r="D79" s="8">
         <f>IF(B79="",0,ROUNDUP(C79*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E79" s="17">
         <f>IF(B79="",0,IFERROR(VLOOKUP(B79,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F79" s="17">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="G79" s="17">
         <f>F79*全局设置!$B$7</f>
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="H79" s="17">
         <f>G79*全局设置!$B$5</f>
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="I79" s="15" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="21.95" customHeight="1">
       <c r="A80" s="16">
         <v>16</v>
       </c>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
+      <c r="B80" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="C80" s="14">
+        <v>100</v>
+      </c>
       <c r="D80" s="8">
         <f>IF(B80="",0,ROUNDUP(C80*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E80" s="17">
         <f>IF(B80="",0,IFERROR(VLOOKUP(B80,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F80" s="17">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="G80" s="17">
         <f>F80*全局设置!$B$7</f>
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="H80" s="17">
         <f>G80*全局设置!$B$5</f>
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="I80" s="15" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="21.95" customHeight="1">
@@ -28417,28 +28455,28 @@
       </c>
       <c r="B84" s="8">
         <f>SUM(C65:C82)</f>
-        <v>176</v>
+        <v>3000</v>
       </c>
       <c r="C84" s="19" t="s">
         <v>124</v>
       </c>
       <c r="D84" s="8">
         <f>SUM(D65:D82)</f>
-        <v>176</v>
+        <v>3000</v>
       </c>
       <c r="E84" s="19" t="s">
         <v>46</v>
       </c>
       <c r="F84" s="8">
         <f>SUM(F65:F82)</f>
-        <v>398</v>
+        <v>47200</v>
       </c>
       <c r="G84" s="19" t="s">
         <v>47</v>
       </c>
       <c r="H84" s="8">
         <f>SUM(G65:G82)</f>
-        <v>398</v>
+        <v>47200</v>
       </c>
       <c r="I84" s="8"/>
     </row>
@@ -28448,19 +28486,19 @@
       </c>
       <c r="B85" s="4">
         <f>SUM(H65:H82)</f>
-        <v>398</v>
+        <v>47200</v>
       </c>
       <c r="C85" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D85" s="41" t="s">
+      <c r="D85" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E85" s="41"/>
-      <c r="F85" s="41"/>
-      <c r="G85" s="41"/>
-      <c r="H85" s="41"/>
-      <c r="I85" s="41"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="40"/>
+      <c r="H85" s="40"/>
+      <c r="I85" s="40"/>
     </row>
     <row r="86" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="87" spans="1:9" ht="21.95" customHeight="1"/>
@@ -28482,17 +28520,17 @@
       <c r="A90" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B90" s="39" t="s">
+      <c r="B90" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="C90" s="39" t="s">
+      <c r="C90" s="41" t="s">
         <v>163</v>
       </c>
       <c r="D90" s="19" t="s">
         <v>103</v>
       </c>
       <c r="E90" s="7">
-        <v>0.22</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F90" s="19" t="s">
         <v>104</v>
@@ -28538,17 +28576,17 @@
       </c>
     </row>
     <row r="92" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A92" s="40" t="s">
+      <c r="A92" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="B92" s="40"/>
-      <c r="C92" s="40"/>
-      <c r="D92" s="40"/>
-      <c r="E92" s="40"/>
-      <c r="F92" s="40"/>
-      <c r="G92" s="40"/>
-      <c r="H92" s="40"/>
-      <c r="I92" s="40"/>
+      <c r="B92" s="39"/>
+      <c r="C92" s="39"/>
+      <c r="D92" s="39"/>
+      <c r="E92" s="39"/>
+      <c r="F92" s="39"/>
+      <c r="G92" s="39"/>
+      <c r="H92" s="39"/>
+      <c r="I92" s="39"/>
     </row>
     <row r="93" spans="1:9" ht="21.95" customHeight="1">
       <c r="A93" s="19" t="s">
@@ -28584,30 +28622,30 @@
         <v>1</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="C94" s="14">
-        <v>53</v>
+        <v>500</v>
       </c>
       <c r="D94" s="8">
         <f>IF(B94="",0,ROUNDUP(C94*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>53</v>
+        <v>500</v>
       </c>
       <c r="E94" s="17">
         <f>IF(B94="",0,IFERROR(VLOOKUP(B94,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F94" s="17">
         <f t="shared" ref="F94:F111" si="6">D94*E94</f>
-        <v>53</v>
+        <v>10000</v>
       </c>
       <c r="G94" s="17">
         <f>F94*全局设置!$B$7</f>
-        <v>53</v>
+        <v>10000</v>
       </c>
       <c r="H94" s="17">
         <f>G94*全局设置!$B$5</f>
-        <v>53</v>
+        <v>10000</v>
       </c>
       <c r="I94" s="15" t="str">
         <f t="shared" ref="I94:I111" si="7">IF(AND(B94="",C94=""),"",IF(AND(B94&lt;&gt;"",C94&gt;=1,COUNTIF($B$94:$B$111,B94)=1),"可回读","需修正"))</f>
@@ -28619,30 +28657,30 @@
         <v>2</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C95" s="14">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="D95" s="8">
         <f>IF(B95="",0,ROUNDUP(C95*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="E95" s="17">
         <f>IF(B95="",0,IFERROR(VLOOKUP(B95,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="17">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>400</v>
       </c>
       <c r="G95" s="17">
         <f>F95*全局设置!$B$7</f>
-        <v>24</v>
+        <v>400</v>
       </c>
       <c r="H95" s="17">
         <f>G95*全局设置!$B$5</f>
-        <v>24</v>
+        <v>400</v>
       </c>
       <c r="I95" s="15" t="str">
         <f t="shared" si="7"/>
@@ -28654,30 +28692,30 @@
         <v>3</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>129</v>
+        <v>463</v>
       </c>
       <c r="C96" s="14">
-        <v>24</v>
+        <v>400</v>
       </c>
       <c r="D96" s="8">
         <f>IF(B96="",0,ROUNDUP(C96*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>24</v>
+        <v>400</v>
       </c>
       <c r="E96" s="17">
         <f>IF(B96="",0,IFERROR(VLOOKUP(B96,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F96" s="17">
         <f t="shared" si="6"/>
-        <v>48</v>
+        <v>4000</v>
       </c>
       <c r="G96" s="17">
         <f>F96*全局设置!$B$7</f>
-        <v>48</v>
+        <v>4000</v>
       </c>
       <c r="H96" s="17">
         <f>G96*全局设置!$B$5</f>
-        <v>48</v>
+        <v>4000</v>
       </c>
       <c r="I96" s="15" t="str">
         <f t="shared" si="7"/>
@@ -28689,30 +28727,30 @@
         <v>4</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>136</v>
+        <v>455</v>
       </c>
       <c r="C97" s="14">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="D97" s="8">
         <f>IF(B97="",0,ROUNDUP(C97*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="E97" s="17">
         <f>IF(B97="",0,IFERROR(VLOOKUP(B97,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F97" s="17">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>4000</v>
       </c>
       <c r="G97" s="17">
         <f>F97*全局设置!$B$7</f>
-        <v>20</v>
+        <v>4000</v>
       </c>
       <c r="H97" s="17">
         <f>G97*全局设置!$B$5</f>
-        <v>20</v>
+        <v>4000</v>
       </c>
       <c r="I97" s="15" t="str">
         <f t="shared" si="7"/>
@@ -28724,30 +28762,30 @@
         <v>5</v>
       </c>
       <c r="B98" s="14" t="s">
-        <v>138</v>
+        <v>447</v>
       </c>
       <c r="C98" s="14">
-        <v>16</v>
+        <v>400</v>
       </c>
       <c r="D98" s="8">
         <f>IF(B98="",0,ROUNDUP(C98*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>16</v>
+        <v>400</v>
       </c>
       <c r="E98" s="17">
         <f>IF(B98="",0,IFERROR(VLOOKUP(B98,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F98" s="17">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>4000</v>
       </c>
       <c r="G98" s="17">
         <f>F98*全局设置!$B$7</f>
-        <v>32</v>
+        <v>4000</v>
       </c>
       <c r="H98" s="17">
         <f>G98*全局设置!$B$5</f>
-        <v>32</v>
+        <v>4000</v>
       </c>
       <c r="I98" s="15" t="str">
         <f t="shared" si="7"/>
@@ -28759,30 +28797,30 @@
         <v>6</v>
       </c>
       <c r="B99" s="14" t="s">
-        <v>122</v>
+        <v>421</v>
       </c>
       <c r="C99" s="14">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D99" s="8">
         <f>IF(B99="",0,ROUNDUP(C99*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E99" s="17">
         <f>IF(B99="",0,IFERROR(VLOOKUP(B99,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F99" s="17">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>10000</v>
       </c>
       <c r="G99" s="17">
         <f>F99*全局设置!$B$7</f>
-        <v>20</v>
+        <v>10000</v>
       </c>
       <c r="H99" s="17">
         <f>G99*全局设置!$B$5</f>
-        <v>20</v>
+        <v>10000</v>
       </c>
       <c r="I99" s="15" t="str">
         <f t="shared" si="7"/>
@@ -28794,30 +28832,30 @@
         <v>7</v>
       </c>
       <c r="B100" s="14" t="s">
-        <v>141</v>
+        <v>475</v>
       </c>
       <c r="C100" s="14">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D100" s="8">
         <f>IF(B100="",0,ROUNDUP(C100*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E100" s="17">
         <f>IF(B100="",0,IFERROR(VLOOKUP(B100,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F100" s="17">
         <f t="shared" si="6"/>
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="G100" s="17">
         <f>F100*全局设置!$B$7</f>
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="H100" s="17">
         <f>G100*全局设置!$B$5</f>
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="I100" s="15" t="str">
         <f t="shared" si="7"/>
@@ -28829,30 +28867,30 @@
         <v>8</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>135</v>
+        <v>404</v>
       </c>
       <c r="C101" s="14">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="D101" s="8">
         <f>IF(B101="",0,ROUNDUP(C101*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="E101" s="17">
         <f>IF(B101="",0,IFERROR(VLOOKUP(B101,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="F101" s="17">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>7000</v>
       </c>
       <c r="G101" s="17">
         <f>F101*全局设置!$B$7</f>
-        <v>32</v>
+        <v>7000</v>
       </c>
       <c r="H101" s="17">
         <f>G101*全局设置!$B$5</f>
-        <v>32</v>
+        <v>7000</v>
       </c>
       <c r="I101" s="15" t="str">
         <f t="shared" si="7"/>
@@ -28864,30 +28902,30 @@
         <v>9</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>144</v>
+        <v>412</v>
       </c>
       <c r="C102" s="14">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D102" s="8">
         <f>IF(B102="",0,ROUNDUP(C102*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="E102" s="17">
         <f>IF(B102="",0,IFERROR(VLOOKUP(B102,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F102" s="17">
         <f t="shared" si="6"/>
-        <v>40</v>
+        <v>7000</v>
       </c>
       <c r="G102" s="17">
         <f>F102*全局设置!$B$7</f>
-        <v>40</v>
+        <v>7000</v>
       </c>
       <c r="H102" s="17">
         <f>G102*全局设置!$B$5</f>
-        <v>40</v>
+        <v>7000</v>
       </c>
       <c r="I102" s="15" t="str">
         <f t="shared" si="7"/>
@@ -28899,30 +28937,30 @@
         <v>10</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>155</v>
+        <v>439</v>
       </c>
       <c r="C103" s="14">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="D103" s="8">
         <f>IF(B103="",0,ROUNDUP(C103*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="E103" s="17">
         <f>IF(B103="",0,IFERROR(VLOOKUP(B103,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F103" s="17">
         <f t="shared" si="6"/>
-        <v>40</v>
+        <v>10000</v>
       </c>
       <c r="G103" s="17">
         <f>F103*全局设置!$B$7</f>
-        <v>40</v>
+        <v>10000</v>
       </c>
       <c r="H103" s="17">
         <f>G103*全局设置!$B$5</f>
-        <v>40</v>
+        <v>10000</v>
       </c>
       <c r="I103" s="15" t="str">
         <f t="shared" si="7"/>
@@ -28934,30 +28972,30 @@
         <v>11</v>
       </c>
       <c r="B104" s="14" t="s">
-        <v>160</v>
+        <v>429</v>
       </c>
       <c r="C104" s="14">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="D104" s="8">
         <f>IF(B104="",0,ROUNDUP(C104*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="E104" s="17">
         <f>IF(B104="",0,IFERROR(VLOOKUP(B104,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F104" s="17">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>2400</v>
       </c>
       <c r="G104" s="17">
         <f>F104*全局设置!$B$7</f>
-        <v>30</v>
+        <v>2400</v>
       </c>
       <c r="H104" s="17">
         <f>G104*全局设置!$B$5</f>
-        <v>30</v>
+        <v>2400</v>
       </c>
       <c r="I104" s="15" t="str">
         <f t="shared" si="7"/>
@@ -28969,30 +29007,30 @@
         <v>12</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>164</v>
+        <v>471</v>
       </c>
       <c r="C105" s="14">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D105" s="8">
         <f>IF(B105="",0,ROUNDUP(C105*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="E105" s="17">
         <f>IF(B105="",0,IFERROR(VLOOKUP(B105,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F105" s="17">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>2000</v>
       </c>
       <c r="G105" s="17">
         <f>F105*全局设置!$B$7</f>
-        <v>24</v>
+        <v>2000</v>
       </c>
       <c r="H105" s="17">
         <f>G105*全局设置!$B$5</f>
-        <v>24</v>
+        <v>2000</v>
       </c>
       <c r="I105" s="15" t="str">
         <f t="shared" si="7"/>
@@ -29004,30 +29042,30 @@
         <v>13</v>
       </c>
       <c r="B106" s="14" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="C106" s="14">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D106" s="8">
         <f>IF(B106="",0,ROUNDUP(C106*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="E106" s="17">
         <f>IF(B106="",0,IFERROR(VLOOKUP(B106,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F106" s="17">
         <f t="shared" si="6"/>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G106" s="17">
         <f>F106*全局设置!$B$7</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="H106" s="17">
         <f>G106*全局设置!$B$5</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I106" s="15" t="str">
         <f t="shared" si="7"/>
@@ -29038,93 +29076,105 @@
       <c r="A107" s="16">
         <v>14</v>
       </c>
-      <c r="B107" s="14"/>
-      <c r="C107" s="14"/>
+      <c r="B107" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C107" s="14">
+        <v>200</v>
+      </c>
       <c r="D107" s="8">
         <f>IF(B107="",0,ROUNDUP(C107*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E107" s="17">
         <f>IF(B107="",0,IFERROR(VLOOKUP(B107,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="17">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G107" s="17">
         <f>F107*全局设置!$B$7</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H107" s="17">
         <f>G107*全局设置!$B$5</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I107" s="15" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="21.95" customHeight="1">
       <c r="A108" s="16">
         <v>15</v>
       </c>
-      <c r="B108" s="14"/>
-      <c r="C108" s="14"/>
+      <c r="B108" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C108" s="14">
+        <v>100</v>
+      </c>
       <c r="D108" s="8">
         <f>IF(B108="",0,ROUNDUP(C108*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E108" s="17">
         <f>IF(B108="",0,IFERROR(VLOOKUP(B108,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F108" s="17">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="G108" s="17">
         <f>F108*全局设置!$B$7</f>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="H108" s="17">
         <f>G108*全局设置!$B$5</f>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="I108" s="15" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="21.95" customHeight="1">
       <c r="A109" s="16">
         <v>16</v>
       </c>
-      <c r="B109" s="14"/>
-      <c r="C109" s="14"/>
+      <c r="B109" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C109" s="14">
+        <v>200</v>
+      </c>
       <c r="D109" s="8">
         <f>IF(B109="",0,ROUNDUP(C109*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E109" s="17">
         <f>IF(B109="",0,IFERROR(VLOOKUP(B109,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F109" s="17">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G109" s="17">
         <f>F109*全局设置!$B$7</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H109" s="17">
         <f>G109*全局设置!$B$5</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I109" s="15" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>可回读</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="21.95" customHeight="1">
@@ -29196,28 +29246,28 @@
       </c>
       <c r="B113" s="8">
         <f>SUM(C94:C111)</f>
-        <v>200</v>
+        <v>4900</v>
       </c>
       <c r="C113" s="19" t="s">
         <v>124</v>
       </c>
       <c r="D113" s="8">
         <f>SUM(D94:D111)</f>
-        <v>200</v>
+        <v>4900</v>
       </c>
       <c r="E113" s="19" t="s">
         <v>46</v>
       </c>
       <c r="F113" s="8">
         <f>SUM(F94:F111)</f>
-        <v>453</v>
+        <v>65000</v>
       </c>
       <c r="G113" s="19" t="s">
         <v>47</v>
       </c>
       <c r="H113" s="8">
         <f>SUM(G94:G111)</f>
-        <v>453</v>
+        <v>65000</v>
       </c>
       <c r="I113" s="8"/>
     </row>
@@ -29227,22 +29277,32 @@
       </c>
       <c r="B114" s="4">
         <f>SUM(H94:H111)</f>
-        <v>453</v>
+        <v>65000</v>
       </c>
       <c r="C114" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D114" s="41" t="s">
+      <c r="D114" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="E114" s="41"/>
-      <c r="F114" s="41"/>
-      <c r="G114" s="41"/>
-      <c r="H114" s="41"/>
-      <c r="I114" s="41"/>
+      <c r="E114" s="40"/>
+      <c r="F114" s="40"/>
+      <c r="G114" s="40"/>
+      <c r="H114" s="40"/>
+      <c r="I114" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="D56:I56"/>
+    <mergeCell ref="A60:I60"/>
     <mergeCell ref="A92:I92"/>
     <mergeCell ref="D114:I114"/>
     <mergeCell ref="B61:C61"/>
@@ -29250,63 +29310,44 @@
     <mergeCell ref="D85:I85"/>
     <mergeCell ref="A89:I89"/>
     <mergeCell ref="B90:C90"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="D56:I56"/>
-    <mergeCell ref="A60:I60"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="D27:I27"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
-  <dataValidations count="14">
-    <dataValidation type="list" sqref="B4 B91 B62 B33">
+  <dataValidations count="11">
+    <dataValidation type="list" sqref="B4 B91 B62 B33" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"点1·开启,点1·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C4 C91 C62 C33">
+    <dataValidation type="list" sqref="C4 C91 C62 C33" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>"点2·开启,点2·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D4 D91 D62 D33">
+    <dataValidation type="list" sqref="D4 D91 D62 D33" xr:uid="{00000000-0002-0000-0500-000002000000}">
       <formula1>"点3·开启,点3·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E4 E91 E62 E33">
+    <dataValidation type="list" sqref="E4 E91 E62 E33" xr:uid="{00000000-0002-0000-0500-000003000000}">
       <formula1>"点4·开启,点4·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F4 F91 F62 F33">
+    <dataValidation type="list" sqref="F4 F91 F62 F33" xr:uid="{00000000-0002-0000-0500-000004000000}">
       <formula1>"点5·开启,点5·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G4 G91 G62 G33">
+    <dataValidation type="list" sqref="G4 G91 G62 G33" xr:uid="{00000000-0002-0000-0500-000005000000}">
       <formula1>"点6·开启,点6·关闭"</formula1>
     </dataValidation>
-    <dataValidation type="whole" sqref="C7:C24 C94:C111 C65:C82 C36:C53">
+    <dataValidation type="whole" sqref="C7:C24 C94:C111 C36:C53 C65:C82" xr:uid="{00000000-0002-0000-0500-000006000000}">
       <formula1>1</formula1>
       <formula2>9999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" sqref="E3 E90 E61 E32">
+    <dataValidation type="decimal" sqref="E3 E90 E32 E61" xr:uid="{00000000-0002-0000-0500-000007000000}">
       <formula1>0.025</formula1>
       <formula2>60</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="G3 G90 G61 G32">
+    <dataValidation type="whole" sqref="G3 G90 G61 G32" xr:uid="{00000000-0002-0000-0500-000008000000}">
       <formula1>1</formula1>
       <formula2>4</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="I3 I90 I61 I32">
+    <dataValidation type="whole" sqref="I3 I90 I61 I32" xr:uid="{00000000-0002-0000-0500-000009000000}">
       <formula1>1</formula1>
       <formula2>999</formula2>
     </dataValidation>
-    <dataValidation type="list" errorStyle="stop" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B7:B24">
-      <formula1>INDIRECT("'敌人目录'!$A$6:$A$68")</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="stop" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B36:B53">
-      <formula1>INDIRECT("'敌人目录'!$A$6:$A$68")</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="stop" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B65:B82">
-      <formula1>INDIRECT("'敌人目录'!$A$6:$A$68")</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="stop" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B94:B111">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="敌人不在目录中" error="请使用单元格下拉列表中的有效敌人。" promptTitle="选择敌人" prompt="请从敌人目录的63名非Boss敌人中选择。" sqref="B36:B53 B94:B111 B7:B24 B65:B82" xr:uid="{00000000-0002-0000-0500-00000A000000}">
       <formula1>INDIRECT("'敌人目录'!$A$6:$A$68")</formula1>
     </dataValidation>
   </dataValidations>
@@ -29400,84 +29441,84 @@
       <c r="A6" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
       <c r="E6" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
     </row>
     <row r="7" spans="1:9" ht="24.95" customHeight="1">
       <c r="A7" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
       <c r="E7" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
     </row>
     <row r="8" spans="1:9" ht="24.95" customHeight="1">
       <c r="A8" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
     </row>
     <row r="9" spans="1:9" ht="24.95" customHeight="1">
       <c r="A9" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
     </row>
     <row r="10" spans="1:9" ht="24.95" customHeight="1">
       <c r="A10" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
     </row>
     <row r="11" spans="1:9" ht="24.95" customHeight="1"/>
     <row r="12" spans="1:9" ht="24.95" customHeight="1">
@@ -29494,56 +29535,61 @@
       <c r="I12" s="33"/>
     </row>
     <row r="13" spans="1:9" ht="32.1" customHeight="1">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="42" t="s">
         <v>187</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
     </row>
     <row r="14" spans="1:9" ht="32.1" customHeight="1">
-      <c r="A14" s="43"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
+      <c r="A14" s="42"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
     </row>
     <row r="15" spans="1:9" ht="32.1" customHeight="1">
-      <c r="A15" s="43"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
+      <c r="A15" s="42"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
     </row>
     <row r="16" spans="1:9" ht="24.95" customHeight="1"/>
     <row r="17" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="F6:I6"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A13:I15"/>
     <mergeCell ref="A17:I17"/>
@@ -29552,11 +29598,6 @@
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F6:I6"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/reports/塔防模式_4日战役智能设计器.xlsx
+++ b/reports/塔防模式_4日战役智能设计器.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R602342835c7e4203"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="2" r:id="R6a966a729708457c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全局设置" sheetId="3" r:id="Re94c2874a8f34c7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第1日" sheetId="4" r:id="Rd2202c147b774552"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第2日" sheetId="5" r:id="Rdadb89cab26f4049"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第3日" sheetId="6" r:id="R78a0e991d01747cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第4日" sheetId="7" r:id="Rb5ff59bb9a384e6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敌人目录" sheetId="8" r:id="R785cb6a314ae4091"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敌人导入数据（勿改）" sheetId="9" r:id="R28b3024e892b4c2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据（勿改）" sheetId="10" r:id="R1f152406f67f43d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统数据（勿改）" sheetId="11" r:id="Rfd0ddd239ab446a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Rb96a82d215e24a8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="2" r:id="R36d0ac61b6ef4ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全局设置" sheetId="3" r:id="Ra7ab0741eaad4105"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第1日" sheetId="4" r:id="R1036c78c97e14229"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第2日" sheetId="5" r:id="R37a259197e704998"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第3日" sheetId="6" r:id="R68dda04c653840be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第4日" sheetId="7" r:id="R3ecd3f7bc2a74bff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敌人目录" sheetId="8" r:id="R38a7c375ddfe4a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敌人导入数据（勿改）" sheetId="9" r:id="R0a833f8e58b54582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据（勿改）" sheetId="10" r:id="Ref5108961a4842d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统数据（勿改）" sheetId="11" r:id="R6fe3ea25c7694dd2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2645,7 +2645,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdadf6ef0c02a4a25"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0984998a573d48f0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2675,7 +2675,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9af6f27ff63a4205"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R61fe7f4aa38b401a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -19440,7 +19440,7 @@
     <x:mergeCell ref="M5:N6"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad68707c99a74342"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f5f75c55dbf4f7f"/>
 </x:worksheet>
 </file>
 
@@ -19752,8 +19752,8 @@
       <x:c r="D3" s="6" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="E3" s="7">
-        <x:v>0.1</x:v>
+      <x:c r="E3" s="7" t="n">
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
         <x:v>101</x:v>
@@ -19764,8 +19764,8 @@
       <x:c r="H3" s="6" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="I3" s="7">
-        <x:v>300</x:v>
+      <x:c r="I3" s="7" t="n">
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="21.950000762939453" customHeight="1">

--- a/reports/塔防模式_4日战役智能设计器.xlsx
+++ b/reports/塔防模式_4日战役智能设计器.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wh\Documents\arc-nice\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E157004F-215F-4D3E-9BDA-86DD40BCF393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031A3AF4-27D1-4F9E-88CF-C0B4E7FF5C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2132,13 +2132,16 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2146,9 +2149,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2264,7 +2264,7 @@
                   <c:v>4050</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4540</c:v>
+                  <c:v>4450</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>5140</c:v>
@@ -2369,7 +2369,7 @@
                   <c:v>4050</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4540</c:v>
+                  <c:v>4450</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>5140</c:v>
@@ -2590,7 +2590,7 @@
                   <c:v>3850</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3470</c:v>
+                  <c:v>3380</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2080</c:v>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="Q45" s="13">
         <f>IF(第1日!B69="","",第1日!C69)</f>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="R45" s="13">
         <v>-1</v>
@@ -18357,19 +18357,19 @@
       <c r="C5" s="41"/>
       <c r="D5" s="41">
         <f>SUM(F9:F20)</f>
-        <v>35530</v>
+        <v>35440</v>
       </c>
       <c r="E5" s="41"/>
       <c r="F5" s="41"/>
       <c r="G5" s="41">
         <f>SUM(G9:G20)</f>
-        <v>35530</v>
+        <v>35440</v>
       </c>
       <c r="H5" s="41"/>
       <c r="I5" s="41"/>
       <c r="J5" s="41">
         <f>SUM(K9:K20)</f>
-        <v>233250</v>
+        <v>233160</v>
       </c>
       <c r="K5" s="41"/>
       <c r="L5" s="41"/>
@@ -18569,11 +18569,11 @@
       </c>
       <c r="F11" s="13">
         <f>SUM(第1日!C65:C82)</f>
-        <v>3470</v>
+        <v>3380</v>
       </c>
       <c r="G11" s="13">
         <f>SUM(第1日!D65:D82)</f>
-        <v>3470</v>
+        <v>3380</v>
       </c>
       <c r="H11" s="13">
         <f>COUNTA(第1日!B65:B82)</f>
@@ -18581,19 +18581,19 @@
       </c>
       <c r="I11" s="17">
         <f>SUM(第1日!F65:F82)</f>
-        <v>4540</v>
+        <v>4450</v>
       </c>
       <c r="J11" s="17">
         <f>SUM(第1日!G65:G82)</f>
-        <v>4540</v>
+        <v>4450</v>
       </c>
       <c r="K11" s="17">
         <f>SUM(第1日!H65:H82)</f>
-        <v>4540</v>
+        <v>4450</v>
       </c>
       <c r="L11" s="13">
         <f>IF(G11=0,0,MAX(0,(ROUNDUP(G11/第1日!G61,0)-1)*第1日!E61))</f>
-        <v>173.4</v>
+        <v>168.9</v>
       </c>
       <c r="M11" s="13">
         <f>第1日!I61</f>
@@ -19166,15 +19166,15 @@
       </c>
       <c r="C26" s="13">
         <f>SUM(F9:F12)</f>
-        <v>12000</v>
+        <v>11910</v>
       </c>
       <c r="D26" s="13">
         <f>SUM(G9:G12)</f>
-        <v>12000</v>
+        <v>11910</v>
       </c>
       <c r="E26" s="13">
         <f>SUM(K9:K12)</f>
-        <v>16330</v>
+        <v>16240</v>
       </c>
       <c r="F26" s="13">
         <f>全局设置!B16</f>
@@ -19295,11 +19295,11 @@
       </c>
       <c r="B36" s="13">
         <f t="shared" si="0"/>
-        <v>4540</v>
+        <v>4450</v>
       </c>
       <c r="C36" s="13">
         <f t="shared" si="1"/>
-        <v>4540</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="23.1" customHeight="1">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="B54" s="13">
         <f t="shared" si="2"/>
-        <v>3470</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="23.1" customHeight="1">
@@ -19855,10 +19855,10 @@
       <c r="A3" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="43" t="s">
         <v>99</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -19911,17 +19911,17 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
     </row>
     <row r="6" spans="1:9" ht="21.95" customHeight="1">
       <c r="A6" s="6" t="s">
@@ -20577,14 +20577,14 @@
       <c r="C27" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="D27" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
     </row>
     <row r="28" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="29" spans="1:9" ht="21.95" customHeight="1"/>
@@ -20606,10 +20606,10 @@
       <c r="A32" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B32" s="45" t="s">
+      <c r="B32" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="45" t="s">
+      <c r="C32" s="43" t="s">
         <v>125</v>
       </c>
       <c r="D32" s="6" t="s">
@@ -20662,17 +20662,17 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A34" s="43" t="s">
+      <c r="A34" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
     </row>
     <row r="35" spans="1:9" ht="21.95" customHeight="1">
       <c r="A35" s="6" t="s">
@@ -21332,14 +21332,14 @@
       <c r="C56" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D56" s="44" t="s">
+      <c r="D56" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E56" s="44"/>
-      <c r="F56" s="44"/>
-      <c r="G56" s="44"/>
-      <c r="H56" s="44"/>
-      <c r="I56" s="44"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="45"/>
+      <c r="G56" s="45"/>
+      <c r="H56" s="45"/>
+      <c r="I56" s="45"/>
     </row>
     <row r="57" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="58" spans="1:9" ht="21.95" customHeight="1"/>
@@ -21361,10 +21361,10 @@
       <c r="A61" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="B61" s="45" t="s">
+      <c r="B61" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="C61" s="45" t="s">
+      <c r="C61" s="43" t="s">
         <v>129</v>
       </c>
       <c r="D61" s="19" t="s">
@@ -21417,17 +21417,17 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A63" s="43" t="s">
+      <c r="A63" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B63" s="43"/>
-      <c r="C63" s="43"/>
-      <c r="D63" s="43"/>
-      <c r="E63" s="43"/>
-      <c r="F63" s="43"/>
-      <c r="G63" s="43"/>
-      <c r="H63" s="43"/>
-      <c r="I63" s="43"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="44"/>
+      <c r="G63" s="44"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="44"/>
     </row>
     <row r="64" spans="1:9" ht="21.95" customHeight="1">
       <c r="A64" s="19" t="s">
@@ -21606,11 +21606,11 @@
         <v>134</v>
       </c>
       <c r="C69" s="14">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D69" s="8">
         <f>IF(B69="",0,ROUNDUP(C69*(1+(全局设置!$B$5-1)*全局设置!$B$6),0))</f>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E69" s="17">
         <f>IF(B69="",0,IFERROR(VLOOKUP(B69,敌人目录!$A$6:$M$68,13,FALSE),0))</f>
@@ -21618,15 +21618,15 @@
       </c>
       <c r="F69" s="17">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G69" s="17">
         <f>F69*全局设置!$B$7</f>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H69" s="17">
         <f>G69*全局设置!$B$5</f>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I69" s="15" t="str">
         <f t="shared" si="5"/>
@@ -22059,28 +22059,28 @@
       </c>
       <c r="B84" s="8">
         <f>SUM(C65:C82)</f>
-        <v>3470</v>
+        <v>3380</v>
       </c>
       <c r="C84" s="19" t="s">
         <v>121</v>
       </c>
       <c r="D84" s="8">
         <f>SUM(D65:D82)</f>
-        <v>3470</v>
+        <v>3380</v>
       </c>
       <c r="E84" s="19" t="s">
         <v>45</v>
       </c>
       <c r="F84" s="8">
         <f>SUM(F65:F82)</f>
-        <v>4540</v>
+        <v>4450</v>
       </c>
       <c r="G84" s="19" t="s">
         <v>46</v>
       </c>
       <c r="H84" s="8">
         <f>SUM(G65:G82)</f>
-        <v>4540</v>
+        <v>4450</v>
       </c>
       <c r="I84" s="8"/>
     </row>
@@ -22090,19 +22090,19 @@
       </c>
       <c r="B85" s="4">
         <f>SUM(H65:H82)</f>
-        <v>4540</v>
+        <v>4450</v>
       </c>
       <c r="C85" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D85" s="44" t="s">
+      <c r="D85" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E85" s="44"/>
-      <c r="F85" s="44"/>
-      <c r="G85" s="44"/>
-      <c r="H85" s="44"/>
-      <c r="I85" s="44"/>
+      <c r="E85" s="45"/>
+      <c r="F85" s="45"/>
+      <c r="G85" s="45"/>
+      <c r="H85" s="45"/>
+      <c r="I85" s="45"/>
     </row>
     <row r="86" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="87" spans="1:9" ht="21.95" customHeight="1"/>
@@ -22124,10 +22124,10 @@
       <c r="A90" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="B90" s="45" t="s">
+      <c r="B90" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="C90" s="45" t="s">
+      <c r="C90" s="43" t="s">
         <v>137</v>
       </c>
       <c r="D90" s="19" t="s">
@@ -22180,17 +22180,17 @@
       </c>
     </row>
     <row r="92" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A92" s="43" t="s">
+      <c r="A92" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B92" s="43"/>
-      <c r="C92" s="43"/>
-      <c r="D92" s="43"/>
-      <c r="E92" s="43"/>
-      <c r="F92" s="43"/>
-      <c r="G92" s="43"/>
-      <c r="H92" s="43"/>
-      <c r="I92" s="43"/>
+      <c r="B92" s="44"/>
+      <c r="C92" s="44"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="44"/>
+      <c r="F92" s="44"/>
+      <c r="G92" s="44"/>
+      <c r="H92" s="44"/>
+      <c r="I92" s="44"/>
     </row>
     <row r="93" spans="1:9" ht="21.95" customHeight="1">
       <c r="A93" s="19" t="s">
@@ -22866,27 +22866,17 @@
       <c r="C114" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D114" s="44" t="s">
+      <c r="D114" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E114" s="44"/>
-      <c r="F114" s="44"/>
-      <c r="G114" s="44"/>
-      <c r="H114" s="44"/>
-      <c r="I114" s="44"/>
+      <c r="E114" s="45"/>
+      <c r="F114" s="45"/>
+      <c r="G114" s="45"/>
+      <c r="H114" s="45"/>
+      <c r="I114" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="D56:I56"/>
-    <mergeCell ref="A60:I60"/>
     <mergeCell ref="A92:I92"/>
     <mergeCell ref="D114:I114"/>
     <mergeCell ref="B61:C61"/>
@@ -22894,6 +22884,16 @@
     <mergeCell ref="D85:I85"/>
     <mergeCell ref="A89:I89"/>
     <mergeCell ref="B90:C90"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="D56:I56"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="D27:I27"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="11">
@@ -22983,10 +22983,10 @@
       <c r="A3" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="43" t="s">
         <v>143</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -23039,17 +23039,17 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
     </row>
     <row r="6" spans="1:9" ht="21.95" customHeight="1">
       <c r="A6" s="6" t="s">
@@ -23741,14 +23741,14 @@
       <c r="C27" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="D27" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
     </row>
     <row r="28" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="29" spans="1:9" ht="21.95" customHeight="1"/>
@@ -23770,10 +23770,10 @@
       <c r="A32" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B32" s="45" t="s">
+      <c r="B32" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="45" t="s">
+      <c r="C32" s="43" t="s">
         <v>150</v>
       </c>
       <c r="D32" s="6" t="s">
@@ -23826,17 +23826,17 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A34" s="43" t="s">
+      <c r="A34" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
     </row>
     <row r="35" spans="1:9" ht="21.95" customHeight="1">
       <c r="A35" s="6" t="s">
@@ -24540,14 +24540,14 @@
       <c r="C56" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D56" s="44" t="s">
+      <c r="D56" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E56" s="44"/>
-      <c r="F56" s="44"/>
-      <c r="G56" s="44"/>
-      <c r="H56" s="44"/>
-      <c r="I56" s="44"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="45"/>
+      <c r="G56" s="45"/>
+      <c r="H56" s="45"/>
+      <c r="I56" s="45"/>
     </row>
     <row r="57" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="58" spans="1:9" ht="21.95" customHeight="1"/>
@@ -24569,10 +24569,10 @@
       <c r="A61" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="B61" s="45" t="s">
+      <c r="B61" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C61" s="45" t="s">
+      <c r="C61" s="43" t="s">
         <v>156</v>
       </c>
       <c r="D61" s="19" t="s">
@@ -24625,17 +24625,17 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A63" s="43" t="s">
+      <c r="A63" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B63" s="43"/>
-      <c r="C63" s="43"/>
-      <c r="D63" s="43"/>
-      <c r="E63" s="43"/>
-      <c r="F63" s="43"/>
-      <c r="G63" s="43"/>
-      <c r="H63" s="43"/>
-      <c r="I63" s="43"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="44"/>
+      <c r="G63" s="44"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="44"/>
     </row>
     <row r="64" spans="1:9" ht="21.95" customHeight="1">
       <c r="A64" s="19" t="s">
@@ -25338,14 +25338,14 @@
       <c r="C85" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D85" s="44" t="s">
+      <c r="D85" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E85" s="44"/>
-      <c r="F85" s="44"/>
-      <c r="G85" s="44"/>
-      <c r="H85" s="44"/>
-      <c r="I85" s="44"/>
+      <c r="E85" s="45"/>
+      <c r="F85" s="45"/>
+      <c r="G85" s="45"/>
+      <c r="H85" s="45"/>
+      <c r="I85" s="45"/>
     </row>
     <row r="86" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="87" spans="1:9" ht="21.95" customHeight="1"/>
@@ -25367,10 +25367,10 @@
       <c r="A90" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="B90" s="45" t="s">
+      <c r="B90" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="C90" s="45" t="s">
+      <c r="C90" s="43" t="s">
         <v>165</v>
       </c>
       <c r="D90" s="19" t="s">
@@ -25423,17 +25423,17 @@
       </c>
     </row>
     <row r="92" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A92" s="43" t="s">
+      <c r="A92" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B92" s="43"/>
-      <c r="C92" s="43"/>
-      <c r="D92" s="43"/>
-      <c r="E92" s="43"/>
-      <c r="F92" s="43"/>
-      <c r="G92" s="43"/>
-      <c r="H92" s="43"/>
-      <c r="I92" s="43"/>
+      <c r="B92" s="44"/>
+      <c r="C92" s="44"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="44"/>
+      <c r="F92" s="44"/>
+      <c r="G92" s="44"/>
+      <c r="H92" s="44"/>
+      <c r="I92" s="44"/>
     </row>
     <row r="93" spans="1:9" ht="21.95" customHeight="1">
       <c r="A93" s="19" t="s">
@@ -26137,27 +26137,17 @@
       <c r="C114" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D114" s="44" t="s">
+      <c r="D114" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E114" s="44"/>
-      <c r="F114" s="44"/>
-      <c r="G114" s="44"/>
-      <c r="H114" s="44"/>
-      <c r="I114" s="44"/>
+      <c r="E114" s="45"/>
+      <c r="F114" s="45"/>
+      <c r="G114" s="45"/>
+      <c r="H114" s="45"/>
+      <c r="I114" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="D56:I56"/>
-    <mergeCell ref="A60:I60"/>
     <mergeCell ref="A92:I92"/>
     <mergeCell ref="D114:I114"/>
     <mergeCell ref="B61:C61"/>
@@ -26165,6 +26155,16 @@
     <mergeCell ref="D85:I85"/>
     <mergeCell ref="A89:I89"/>
     <mergeCell ref="B90:C90"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="D56:I56"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="D27:I27"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="11">
@@ -26254,10 +26254,10 @@
       <c r="A3" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="43" t="s">
         <v>173</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -26310,17 +26310,17 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
     </row>
     <row r="6" spans="1:9" ht="21.95" customHeight="1">
       <c r="A6" s="6" t="s">
@@ -27004,14 +27004,14 @@
       <c r="C27" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="D27" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
     </row>
     <row r="28" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="29" spans="1:9" ht="21.95" customHeight="1"/>
@@ -27033,10 +27033,10 @@
       <c r="A32" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B32" s="45" t="s">
+      <c r="B32" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="45" t="s">
+      <c r="C32" s="43" t="s">
         <v>177</v>
       </c>
       <c r="D32" s="6" t="s">
@@ -27089,17 +27089,17 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A34" s="43" t="s">
+      <c r="A34" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
     </row>
     <row r="35" spans="1:9" ht="21.95" customHeight="1">
       <c r="A35" s="6" t="s">
@@ -27791,14 +27791,14 @@
       <c r="C56" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D56" s="44" t="s">
+      <c r="D56" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E56" s="44"/>
-      <c r="F56" s="44"/>
-      <c r="G56" s="44"/>
-      <c r="H56" s="44"/>
-      <c r="I56" s="44"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="45"/>
+      <c r="G56" s="45"/>
+      <c r="H56" s="45"/>
+      <c r="I56" s="45"/>
     </row>
     <row r="57" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="58" spans="1:9" ht="21.95" customHeight="1"/>
@@ -27820,10 +27820,10 @@
       <c r="A61" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="B61" s="45" t="s">
+      <c r="B61" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C61" s="45" t="s">
+      <c r="C61" s="43" t="s">
         <v>179</v>
       </c>
       <c r="D61" s="19" t="s">
@@ -27876,17 +27876,17 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A63" s="43" t="s">
+      <c r="A63" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B63" s="43"/>
-      <c r="C63" s="43"/>
-      <c r="D63" s="43"/>
-      <c r="E63" s="43"/>
-      <c r="F63" s="43"/>
-      <c r="G63" s="43"/>
-      <c r="H63" s="43"/>
-      <c r="I63" s="43"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="44"/>
+      <c r="G63" s="44"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="44"/>
     </row>
     <row r="64" spans="1:9" ht="21.95" customHeight="1">
       <c r="A64" s="19" t="s">
@@ -28582,14 +28582,14 @@
       <c r="C85" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D85" s="44" t="s">
+      <c r="D85" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E85" s="44"/>
-      <c r="F85" s="44"/>
-      <c r="G85" s="44"/>
-      <c r="H85" s="44"/>
-      <c r="I85" s="44"/>
+      <c r="E85" s="45"/>
+      <c r="F85" s="45"/>
+      <c r="G85" s="45"/>
+      <c r="H85" s="45"/>
+      <c r="I85" s="45"/>
     </row>
     <row r="86" spans="1:9" ht="21.95" customHeight="1"/>
     <row r="87" spans="1:9" ht="21.95" customHeight="1"/>
@@ -28611,10 +28611,10 @@
       <c r="A90" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="B90" s="45" t="s">
+      <c r="B90" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C90" s="45" t="s">
+      <c r="C90" s="43" t="s">
         <v>181</v>
       </c>
       <c r="D90" s="19" t="s">
@@ -28667,17 +28667,17 @@
       </c>
     </row>
     <row r="92" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A92" s="43" t="s">
+      <c r="A92" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B92" s="43"/>
-      <c r="C92" s="43"/>
-      <c r="D92" s="43"/>
-      <c r="E92" s="43"/>
-      <c r="F92" s="43"/>
-      <c r="G92" s="43"/>
-      <c r="H92" s="43"/>
-      <c r="I92" s="43"/>
+      <c r="B92" s="44"/>
+      <c r="C92" s="44"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="44"/>
+      <c r="F92" s="44"/>
+      <c r="G92" s="44"/>
+      <c r="H92" s="44"/>
+      <c r="I92" s="44"/>
     </row>
     <row r="93" spans="1:9" ht="21.95" customHeight="1">
       <c r="A93" s="19" t="s">
@@ -29373,27 +29373,17 @@
       <c r="C114" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D114" s="44" t="s">
+      <c r="D114" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E114" s="44"/>
-      <c r="F114" s="44"/>
-      <c r="G114" s="44"/>
-      <c r="H114" s="44"/>
-      <c r="I114" s="44"/>
+      <c r="E114" s="45"/>
+      <c r="F114" s="45"/>
+      <c r="G114" s="45"/>
+      <c r="H114" s="45"/>
+      <c r="I114" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="D56:I56"/>
-    <mergeCell ref="A60:I60"/>
     <mergeCell ref="A92:I92"/>
     <mergeCell ref="D114:I114"/>
     <mergeCell ref="B61:C61"/>
@@ -29401,6 +29391,16 @@
     <mergeCell ref="D85:I85"/>
     <mergeCell ref="A89:I89"/>
     <mergeCell ref="B90:C90"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="D56:I56"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="D27:I27"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="11">
@@ -29532,84 +29532,84 @@
       <c r="A6" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="46" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
       <c r="E6" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
     </row>
     <row r="7" spans="1:9" ht="24.95" customHeight="1">
       <c r="A7" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
       <c r="E7" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="46" t="s">
         <v>195</v>
       </c>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
     </row>
     <row r="8" spans="1:9" ht="24.95" customHeight="1">
       <c r="A8" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
     </row>
     <row r="9" spans="1:9" ht="24.95" customHeight="1">
       <c r="A9" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="46" t="s">
         <v>199</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
     </row>
     <row r="10" spans="1:9" ht="24.95" customHeight="1">
       <c r="A10" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
     </row>
     <row r="11" spans="1:9" ht="24.95" customHeight="1"/>
     <row r="12" spans="1:9" ht="24.95" customHeight="1">
@@ -29626,61 +29626,56 @@
       <c r="I12" s="37"/>
     </row>
     <row r="13" spans="1:9" ht="32.1" customHeight="1">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="47" t="s">
         <v>203</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
     </row>
     <row r="14" spans="1:9" ht="32.1" customHeight="1">
-      <c r="A14" s="46"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
+      <c r="A14" s="47"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
     </row>
     <row r="15" spans="1:9" ht="32.1" customHeight="1">
-      <c r="A15" s="46"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
+      <c r="A15" s="47"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
     </row>
     <row r="16" spans="1:9" ht="24.95" customHeight="1"/>
     <row r="17" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A17" s="47" t="s">
+      <c r="A17" s="48" t="s">
         <v>204</v>
       </c>
-      <c r="B17" s="47"/>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F6:I6"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A13:I15"/>
     <mergeCell ref="A17:I17"/>
@@ -29689,6 +29684,11 @@
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B10:I10"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="F6:I6"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
